--- a/content/Question Bank/Coding Questions/Unit 4 - Looping/Unit 4 - Looping - Coding Questions.xlsx
+++ b/content/Question Bank/Coding Questions/Unit 4 - Looping/Unit 4 - Looping - Coding Questions.xlsx
@@ -596,7 +596,8 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>A launch console counts down before lift-off. Read N and print every number from N down to 1, one per line.
+          <t>The science club is launching its model rocket at the tech fest, and the big screen must count down dramatically before lift-off. The countdown starts at whatever number the operator types in and ticks all the way down to 1.
+Write a program that reads a whole number `N` and uses a loop to print every number from `N` down to 1, one number per line.
 ### Input Format
 - Line 1: N, the starting number
 ### Output Format
@@ -607,6 +608,8 @@
 2
 1
 ```
+### Example Walkthrough
+In the sample, `N` is 5. The loop starts at 5 and prints it, then steps down one at a time - 4, then 3, then 2 - and stops after printing `1`. That gives five lines in decreasing order.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -770,13 +773,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>A spelling game counts the vowels in a word. Read one line of text and print how many vowels (a, e, i, o, u) it contains, ignoring case.
+          <t>A spelling game at the school fest awards a point for every vowel in the word a player types. The game needs a counter that scans the word letter by letter and keeps a running total.
+Write a program that reads one line of text and prints how many vowels (`a`, `e`, `i`, `o`, `u`) it contains. Count capital and small letters alike - `A` and `a` are both vowels.
 ### Input Format
 - Line 1: A line of text
 ### Output Format
 ```
 5
 ```
+### Example Walkthrough
+In the sample, the input is `education`. Scanning it letter by letter, the vowels found are `e`, `u`, `a`, `i`, and `o` - five in total - so the program prints `5`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -918,7 +924,8 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>A maths tutor app prints the multiplication table of a number. Read N and print its table from 1 to 10 in the form 'N x i = value'.
+          <t>Ravi is helping his younger sister memorise multiplication tables, and he builds a small app that prints any table on demand. She types a number, and the full table from 1 to 10 appears instantly.
+Write a program that reads a whole number `N` and prints its multiplication table from 1 to 10, one line per product, in the exact form `N x i = value` with single spaces around the `x` and the `=`.
 ### Input Format
 - Line 1: N, the number
 ### Output Format
@@ -934,6 +941,8 @@
 2 x 9 = 18
 2 x 10 = 20
 ```
+### Example Walkthrough
+In the sample, `N` is 2. The loop runs `i` from 1 to 10, printing `2 x 1 = 2` first, then `2 x 2 = 4`, and so on, ending with `2 x 10 = 20` - ten lines in all.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1135,13 +1144,16 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A form validator counts how many digits a number has. Read a whole number and print the number of digits it contains.
+          <t>A form validator on a payment page needs to know how many digits a customer's number has before accepting it. The developer counts the digits the classic way: repeatedly chopping off the last digit until nothing is left, counting one chop each time.
+Write a program that reads a whole number and prints how many digits it contains.
 ### Input Format
 - Line 1: A whole number
 ### Output Format
 ```
 5
 ```
+### Example Walkthrough
+In the sample, the number is 12345. Chopping off the last digit repeatedly gives 1234, then 123, then 12, then 1, then 0 - five chops in total - so the number has 5 digits and the program prints `5`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1286,7 +1298,8 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Print the numbers 1 to N, but replace multiples of 3 with 'Fizz', multiples of 5 with 'Buzz', and multiples of both with 'FizzBuzz'. Print one value per line.
+          <t>In a classic classroom counting game, players count upward from 1, but any number divisible by 3 is replaced with `Fizz`, any number divisible by 5 with `Buzz`, and any number divisible by both with `FizzBuzz`. Your job is to teach the computer to play a full round on its own.
+Write a program that reads a whole number `N` and prints the sequence from 1 to `N`, one value per line, applying the three replacement rules. Remember to check the "divisible by both" case first.
 ### Input Format
 - Line 1: N
 ### Output Format
@@ -1297,6 +1310,8 @@
 4
 Buzz
 ```
+### Example Walkthrough
+In the sample, `N` is 5. The numbers 1 and 2 are printed as they are; 3 is divisible by 3, so `Fizz` appears in its place; 4 is printed normally; and 5 is divisible by 5, so the round ends with `Buzz`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1554,13 +1569,16 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>A checksum tool adds up the digits of a number. Read a whole number and print the sum of its digits.
+          <t>A courier company's tracking codes end with a checksum - a small number made by adding up all the digits of the code. Before a parcel is booked, the system must work out this digit sum to verify the code.
+Write a program that reads a whole number and prints the sum of its digits. Use a loop that repeatedly takes the last digit (the remainder when dividing by 10, i.e. what is left over) and then removes that digit from the number.
 ### Input Format
 - Line 1: A whole number
 ### Output Format
 ```
 10
 ```
+### Example Walkthrough
+In the sample, the number is 1234. Its digits are 1, 2, 3, and 4, and adding them gives 1 + 2 + 3 + 4 = 10, so the program prints `10`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1702,7 +1720,8 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Read two whole numbers and print their greatest common divisor using repeated remainders (Euclid's method).
+          <t>For the fest decorations, Kiran has two ribbon rolls - one 12 metres long and one 18 metres long - and wants to cut both into equal pieces that are as long as possible with nothing wasted. The answer is the greatest common divisor (GCD): the largest number that divides both lengths exactly.
+Write a program that reads two whole numbers and prints their GCD using Euclid's method of repeated remainders: keep dividing and taking the remainder until the remainder becomes 0; the last non-zero value is the answer.
 ### Input Format
 - Line 1: First number
 - Line 2: Second number
@@ -1710,6 +1729,8 @@
 ```
 6
 ```
+### Example Walkthrough
+In the sample, the numbers are 12 and 18. Dividing 18 by 12 leaves a remainder of 6; dividing 12 by 6 leaves a remainder of 0, so the process stops and the GCD is 6. Ribbon pieces of 6 metres use up both rolls perfectly, and the program prints `6`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1857,13 +1878,16 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Read a whole number and print 'Prime' if it is a prime number, otherwise print 'Not Prime'.
+          <t>In the maths club's number game, a player shouts out a number and the club's app must instantly say whether it is prime. A prime number is a whole number greater than 1 that no smaller number (except 1) divides exactly - 7 is prime, but 8 is not, because 2 divides it.
+Write a program that reads a whole number and prints exactly `Prime` if it is a prime number, and exactly `Not Prime` otherwise. Use a loop to test the possible divisors.
 ### Input Format
 - Line 1: A whole number
 ### Output Format
 ```
 Prime
 ```
+### Example Walkthrough
+In the sample, the number is 7. Testing the possible divisors 2, 3, 4, 5, and 6, none of them divides 7 without a remainder, so 7 is prime and the program prints `Prime`. A number like 9 would be caught by 3 and print `Not Prime`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -2009,7 +2033,8 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Print a left-aligned right triangle of stars with N rows: row i has i stars.
+          <t>For the freshers' party, the decoration team is sticking star-shaped stickers on the staircase wall: one star on the top row, two on the next, and so on, growing by one star each row. They want a program that previews the pattern for any height.
+Write a program that reads a whole number `N` and prints `N` rows of stars, where row 1 has one star, row 2 has two stars, and in general row `i` has `i` stars, with no spaces in between.
 ### Input Format
 - Line 1: N, the number of rows
 ### Output Format
@@ -2019,6 +2044,8 @@
 ***
 ****
 ```
+### Example Walkthrough
+In the sample, `N` is 4. The loop prints one star on the first line, two on the second, three on the third, and four on the fourth, producing a staircase that grows by exactly one star per row.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -2172,7 +2199,8 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Print Floyd's triangle with N rows: fill consecutive counting numbers starting at 1, where row i contains i numbers.
+          <t>On the whiteboard in the coding club, someone has drawn Floyd's triangle: the counting numbers written out in rows, where each row holds one more number than the row above, and the counting never restarts. The club wants a program that prints the triangle for any number of rows.
+Write a program that reads a whole number `N` and prints `N` rows: row 1 has one number, row 2 has the next two, row 3 the next three, and so on, starting the count from 1 and separating the numbers in a row with single spaces.
 ### Input Format
 - Line 1: N
 ### Output Format
@@ -2181,6 +2209,8 @@
 2 3
 4 5 6
 ```
+### Example Walkthrough
+In the sample, `N` is 3. The counter starts at 1: row 1 takes just `1`; row 2 takes the next two numbers, `2 3`; and row 3 takes the following three, `4 5 6`. Six numbers are used in total, in unbroken counting order.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>

--- a/content/Question Bank/Coding Questions/Unit 4 - Looping/Unit 4 - Looping - Coding Questions.xlsx
+++ b/content/Question Bank/Coding Questions/Unit 4 - Looping/Unit 4 - Looping - Coding Questions.xlsx
@@ -1,13 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 4" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH31"/>
+  <dimension ref="A1:AH11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -625,22 +628,32 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>loops</t>
+          <t>loops-and-iteration</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>for-loops</t>
+          <t>for-loops-and-range</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -798,22 +811,32 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>loops</t>
+          <t>loops-and-iteration</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>for-loops</t>
+          <t>common-loop-patterns</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -958,22 +981,32 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>loops</t>
+          <t>loops-and-iteration</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>for-loops</t>
+          <t>for-loops-and-range</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1169,17 +1202,27 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>loops</t>
+          <t>loops-and-iteration</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1327,22 +1370,32 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>loops</t>
+          <t>loops-and-iteration</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>for-loops</t>
+          <t>for-loops-and-range</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1594,17 +1647,27 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>loops</t>
+          <t>loops-and-iteration</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1746,17 +1809,27 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>loops</t>
+          <t>loops-and-iteration</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1903,22 +1976,32 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>loops</t>
+          <t>loops-and-iteration</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>for-loops</t>
+          <t>loop-control-statements</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -2028,10 +2111,521 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Python - Sum First N</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Sum First N. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: N
+### Output Format
+```
+15
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>loops-and-iteration</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>for-loops-and-range</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>1</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>5050</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>n=int(input())
+t=0
+for i in range(1,n+1): t+=i
+print(t)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Python - Print Countdown</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Print Countdown. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: N
+### Output Format
+```
+3
+2
+1
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>loops-and-iteration</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>while-loops</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>1</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>3
+2
+1</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>5
+4
+3
+2
+1</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>7
+6
+5
+4
+3
+2
+1</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2
+1</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>4
+3
+2
+1</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>n=int(input())
+while n&gt;0:
+ print(n); n-=1</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AH11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>explanation</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>difficulty</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>bloomTaxonomy</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>subjects</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>topics</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>subTopics</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>companies</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>codingType</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>supportAllLanguages</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>enablePartialScore</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ignoreCase</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>testcase1_input</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>testcase1_output</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>testcase2_input</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>testcase2_output</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>testcase3_input</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>testcase3_output</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>testcase4_input</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>testcase4_output</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>testcase5_input</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>testcase5_output</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>testcase6_input</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>testcase6_output</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>testcase7_input</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>testcase7_output</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>preloadCode_python</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>solution_python</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>hints</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
           <t>Python - Star Staircase</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>For the freshers' party, the decoration team is sticking star-shaped stickers on the staircase wall: one star on the top row, two on the next, and so on, growing by one star each row. They want a program that previews the pattern for any height.
 Write a program that reads a whole number `N` and prints `N` rows of stars, where row 1 has one star, row 2 has two stars, and in general row `i` has `i` stars, with no spaces in between.
@@ -2051,59 +2645,69 @@
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D2" t="n">
         <v>5</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>loops</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>nested-loops</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>loops-and-iteration</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>for-loops-and-range</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O10" t="b">
+      <c r="O2" t="b">
         <v>0</v>
       </c>
-      <c r="P10" t="b">
+      <c r="P2" t="b">
         <v>1</v>
       </c>
-      <c r="Q10" t="b">
+      <c r="Q2" t="b">
         <v>1</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>*
 **
@@ -2111,22 +2715,22 @@
 ****</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>*</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>*
 **
@@ -2135,28 +2739,28 @@
 *****</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>*
 **</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>*
 **
@@ -2168,12 +2772,12 @@
 ********</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>*
 **
@@ -2183,7 +2787,7 @@
 ******</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>n = int(input())
 for i in range(1, n + 1):
@@ -2191,13 +2795,13 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Python - Floyd's Triangle</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>On the whiteboard in the coding club, someone has drawn Floyd's triangle: the counting numbers written out in rows, where each row holds one more number than the row above, and the counting never restarts. The club wants a program that prints the triangle for any number of rows.
 Write a program that reads a whole number `N` and prints `N` rows: row 1 has one number, row 2 has the next two, row 3 the next three, and so on, starting the count from 1 and separating the numbers in a row with single spaces.
@@ -2216,81 +2820,91 @@
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D3" t="n">
         <v>5</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>loops</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>loops-and-iteration</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>nested-loops</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O11" t="b">
+      <c r="O3" t="b">
         <v>0</v>
       </c>
-      <c r="P11" t="b">
+      <c r="P3" t="b">
         <v>1</v>
       </c>
-      <c r="Q11" t="b">
+      <c r="Q3" t="b">
         <v>1</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>1
 2 3
 4 5 6</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>1
 2 3
@@ -2298,28 +2912,28 @@
 7 8 9 10</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>1
 2 3</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1
 2 3
@@ -2329,12 +2943,12 @@
 16 17 18 19 20 21</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>1
 2 3
@@ -2343,7 +2957,7 @@
 11 12 13 14 15</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>n = int(input())
 num = 1
@@ -2356,144 +2970,156 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Python - Daily Steps Total</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>A fitness app adds up a running total from day 1 to day N. Read N and print the sum of all whole numbers from 1 to N.
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>A fitness app adds up a running total from day 1 to day `N`. Read `N` and print the sum of all whole numbers from 1 to `N`.
 ### Input Format
 - Line 1: N, the number of days
 ### Output Format
 ```
 15
 ```
+### Example Walkthrough
+In the sample, `N` is `5`. Summing `1 + 2 + 3 + 4 + 5` gives `15`, so the program prints `15`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D4" t="n">
         <v>5</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>loops</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>for-loops</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>loops-and-iteration</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>common-loop-patterns</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O12" t="b">
+      <c r="O4" t="b">
         <v>0</v>
       </c>
-      <c r="P12" t="b">
+      <c r="P4" t="b">
         <v>1</v>
       </c>
-      <c r="Q12" t="b">
+      <c r="Q4" t="b">
         <v>1</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>210</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1275</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AE12" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="AG12" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>n = int(input())
 total = 0
@@ -2503,15 +3129,15 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Python - Cash Register Total</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>A shop till adds up the prices of N items. Read N, then read N prices on separate lines and print their total.
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>A shop till adds up the prices of `N` items. Read `N`, then read `N` prices on separate lines and print their total.
 ### Input Format
 - Line 1: N, the number of items
 - Next N lines: one price each
@@ -2519,59 +3145,71 @@
 ```
 60
 ```
+### Example Walkthrough
+In the sample, `N` is `3` with prices `10`, `20`, and `30`. Adding them gives `60`, so the program prints `60`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D5" t="n">
         <v>5</v>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>loops</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>for-loops</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>loops-and-iteration</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>common-loop-patterns</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O13" t="b">
+      <c r="O5" t="b">
         <v>0</v>
       </c>
-      <c r="P13" t="b">
+      <c r="P5" t="b">
         <v>1</v>
       </c>
-      <c r="Q13" t="b">
+      <c r="Q5" t="b">
         <v>1</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>3
 10
@@ -2579,23 +3217,23 @@
 30</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>1
 5</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>4
 1
@@ -2604,24 +3242,24 @@
 4</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>2
 0
 0</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>5
 100
@@ -2631,23 +3269,23 @@
 500</t>
         </is>
       </c>
-      <c r="AA13" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>1500</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>1
 999</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="AD13" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>6
 1
@@ -2658,12 +3296,12 @@
 1</t>
         </is>
       </c>
-      <c r="AE13" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AG13" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>n = int(input())
 total = 0
@@ -2673,144 +3311,156 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Python - Factorial Machine</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>A calculator computes the factorial of N (the product 1 x 2 x ... x N; 0! is 1). Read N and print N!.
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>A calculator computes the factorial of `N` (the product `1 x 2 x ... x N`; `0!` is `1`). Read `N` and print `N!`.
 ### Input Format
 - Line 1: N
 ### Output Format
 ```
 120
 ```
+### Example Walkthrough
+In the sample, `N` is `5`. Multiplying `1 x 2 x 3 x 4 x 5` gives `120`, so the program prints `120`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="D6" t="n">
         <v>5</v>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>loops</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>for-loops</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>loops-and-iteration</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>common-loop-patterns</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O14" t="b">
+      <c r="O6" t="b">
         <v>0</v>
       </c>
-      <c r="P14" t="b">
+      <c r="P6" t="b">
         <v>1</v>
       </c>
-      <c r="Q14" t="b">
+      <c r="Q6" t="b">
         <v>1</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>120</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>720</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA14" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>5040</t>
         </is>
       </c>
-      <c r="AD14" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AE14" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>3628800</t>
         </is>
       </c>
-      <c r="AG14" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>n = int(input())
 fact = 1
@@ -2820,15 +3470,15 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Python - Even Numbers List</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>A number-line poster shows all even numbers up to a limit. Read N and print every even number from 2 up to N, one per line.
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>A number-line poster shows all even numbers up to a limit. Read `N` and print every even number from 2 up to `N`, one per line.
 ### Input Format
 - Line 1: N, the upper limit
 ### Output Format
@@ -2839,64 +3489,76 @@
 8
 10
 ```
+### Example Walkthrough
+In the sample, `N` is `10`. The even numbers from `2` up to `10` are `2, 4, 6, 8, 10`, each printed on its own line.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D7" t="n">
         <v>5</v>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>loops</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>for-loops</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>loops-and-iteration</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>for-loops-and-range</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O15" t="b">
+      <c r="O7" t="b">
         <v>0</v>
       </c>
-      <c r="P15" t="b">
+      <c r="P7" t="b">
         <v>1</v>
       </c>
-      <c r="Q15" t="b">
+      <c r="Q7" t="b">
         <v>1</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>2
 4
@@ -2905,12 +3567,12 @@
 10</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>2
 4
@@ -2918,32 +3580,32 @@
 8</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>2
 4
@@ -2957,12 +3619,12 @@
 20</t>
         </is>
       </c>
-      <c r="AD15" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="AE15" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>2
 4
@@ -2973,7 +3635,7 @@
 14</t>
         </is>
       </c>
-      <c r="AG15" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>n = int(input())
 for i in range(2, n + 1, 2):
@@ -2981,15 +3643,15 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Python - Class Average</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>A teacher averages N test scores. Read N, then read N scores on separate lines and print their average rounded to 2 decimal places.
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>A teacher averages `N` test scores. Read `N`, then read `N` scores on separate lines and print their average rounded to 2 decimal places.
 ### Input Format
 - Line 1: N
 - Next N lines: one score each
@@ -2997,59 +3659,71 @@
 ```
 80.0
 ```
+### Example Walkthrough
+In the sample, `N` is `3` with scores `70`, `80`, and `90`. Their average is `(70 + 80 + 90) / 3 = 80.0`, so the program prints `80.0`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="D8" t="n">
         <v>5</v>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>loops</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>for-loops</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>loops-and-iteration</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>common-loop-patterns</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O16" t="b">
+      <c r="O8" t="b">
         <v>0</v>
       </c>
-      <c r="P16" t="b">
+      <c r="P8" t="b">
         <v>1</v>
       </c>
-      <c r="Q16" t="b">
+      <c r="Q8" t="b">
         <v>1</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>3
 80
@@ -3057,46 +3731,46 @@
 70</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>80.0</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>2
 50
 75</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>62.5</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>1
 42</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>42.0</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>1
 0</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>4
 60
@@ -3105,12 +3779,12 @@
 90</t>
         </is>
       </c>
-      <c r="AA16" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>75.0</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>5
 100
@@ -3120,24 +3794,24 @@
 100</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AD16" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>2
 33
 67</t>
         </is>
       </c>
-      <c r="AE16" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>50.0</t>
         </is>
       </c>
-      <c r="AG16" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>n = int(input())
 total = 0
@@ -3147,13 +3821,13 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Python - String Reverser</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>A word-game shows a word spelled backwards. Read one line and print its characters in reverse order, building the result with a loop.
 ### Input Format
@@ -3162,129 +3836,141 @@
 ```
 olleh
 ```
+### Example Walkthrough
+In the sample, the input is `hello`. Reversing its characters gives `olleh`, so the program prints `olleh`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D9" t="n">
         <v>5</v>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>loops</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>for-loops</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>loops-and-iteration</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>sequence-iteration</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O17" t="b">
+      <c r="O9" t="b">
         <v>0</v>
       </c>
-      <c r="P17" t="b">
+      <c r="P9" t="b">
         <v>1</v>
       </c>
-      <c r="Q17" t="b">
+      <c r="Q9" t="b">
         <v>1</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>hello</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>olleh</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>level</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>level</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>nohtyP</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>racecar</t>
         </is>
       </c>
-      <c r="AA17" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>racecar</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>OpenAI</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>IAnepO</t>
         </is>
       </c>
-      <c r="AD17" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>Coding</t>
         </is>
       </c>
-      <c r="AE17" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>gnidoC</t>
         </is>
       </c>
-      <c r="AG17" t="inlineStr">
+      <c r="AG9" t="inlineStr">
         <is>
           <t>text = input()
 result = ""
@@ -3294,144 +3980,653 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Python - Count Letter A</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Count Letter A. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Text
+### Output Format
+```
+3
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>loops-and-iteration</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>sequence-iteration</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>1</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>banana</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>apple</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>xyz</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>aaaa</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>Ananya</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>s=input()
+c=0
+for ch in s:
+ if ch=="a": c+=1
+print(c)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Python - Multiples List</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Multiples List. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: N
+### Output Format
+```
+2 4 6 8 10
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>loops-and-iteration</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>for-loops-and-range</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>1</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>2 4 6 8 10</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>5 10 15 20 25</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>1 2 3 4 5</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>0 0 0 0 0</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>-3</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>-3 -6 -9 -12 -15</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>10 20 30 40 50</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>7 14 21 28 35</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>n=int(input())
+print(*[n*i for i in range(1,6)])</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AH11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>explanation</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>difficulty</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>bloomTaxonomy</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>subjects</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>topics</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>subTopics</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>companies</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>codingType</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>supportAllLanguages</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>enablePartialScore</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ignoreCase</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>testcase1_input</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>testcase1_output</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>testcase2_input</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>testcase2_output</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>testcase3_input</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>testcase3_output</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>testcase4_input</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>testcase4_output</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>testcase5_input</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>testcase5_output</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>testcase6_input</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>testcase6_output</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>testcase7_input</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>testcase7_output</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>preloadCode_python</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>solution_python</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>hints</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Python - Sum of Even Numbers</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>An energy meter sums only the even readings from 1 to N. Read N and print the total of all even numbers in that range.
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>An energy meter sums only the even readings from 1 to `N`. Read `N` and print the total of all even numbers in that range.
 ### Input Format
 - Line 1: N
 ### Output Format
 ```
 30
 ```
+### Example Walkthrough
+In the sample, `N` is `10`. The even numbers up to `10` are `2, 4, 6, 8, 10`, which add up to `30`, so the program prints `30`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="D2" t="n">
         <v>5</v>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>loops</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>for-loops</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>loops-and-iteration</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>common-loop-patterns</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O18" t="b">
+      <c r="O2" t="b">
         <v>0</v>
       </c>
-      <c r="P18" t="b">
+      <c r="P2" t="b">
         <v>1</v>
       </c>
-      <c r="Q18" t="b">
+      <c r="Q2" t="b">
         <v>1</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA18" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>110</t>
         </is>
       </c>
-      <c r="AD18" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AE18" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="AG18" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>n = int(input())
 total = 0
@@ -3442,15 +4637,15 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Python - Above the Bar</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>A results board counts how many scores beat a cut-off. Read N, then a line of N scores, then the cut-off, and print how many scores are strictly greater than the cut-off.
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>A results board counts how many scores beat a cut-off. Read `N`, then a line of `N` scores, then the cut-off, and print how many scores are strictly greater than the cut-off.
 ### Input Format
 - Line 1: N
 - Line 2: N space-separated scores
@@ -3459,143 +4654,155 @@
 ```
 3
 ```
+### Example Walkthrough
+In the sample, `N` is `5` with scores `50 60 70 80 90` and a cut-off of `65`. The scores strictly greater than `65` are `70`, `80`, and `90` - three in total - so the program prints `3`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="D3" t="n">
         <v>5</v>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>loops</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>for-loops</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>loops-and-iteration</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>common-loop-patterns</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O19" t="b">
+      <c r="O3" t="b">
         <v>0</v>
       </c>
-      <c r="P19" t="b">
+      <c r="P3" t="b">
         <v>1</v>
       </c>
-      <c r="Q19" t="b">
+      <c r="Q3" t="b">
         <v>1</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>5
 10 20 30 40 50
 25</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>3
 1 2 3
 5</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>4
 7 8 9 10
 8</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>1
 5
 0</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>6
 -1 -2 3 4 5 6
 2</t>
         </is>
       </c>
-      <c r="AA19" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>3
 100 200 300
 1000</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AD19" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>2
 5 5
 5</t>
         </is>
       </c>
-      <c r="AE19" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AG19" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>n = int(input())
 nums = list(map(int, input().split()))
@@ -3608,15 +4815,15 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Python - Highest Reading</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>A weather log finds the highest temperature of the day. Read N, then a line of N temperatures, and print the largest one using a loop.
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>A weather log finds the highest temperature of the day. Read `N`, then a line of `N` temperatures, and print the largest one using a loop.
 ### Input Format
 - Line 1: N
 - Line 2: N space-separated numbers
@@ -3624,136 +4831,148 @@
 ```
 9
 ```
+### Example Walkthrough
+In the sample, `N` is `4` with readings `3 9 5 1`. The largest of these is `9`, so the program prints `9`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="D4" t="n">
         <v>5</v>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>loops</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>for-loops</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>loops-and-iteration</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>common-loop-patterns</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O20" t="b">
+      <c r="O4" t="b">
         <v>0</v>
       </c>
-      <c r="P20" t="b">
+      <c r="P4" t="b">
         <v>1</v>
       </c>
-      <c r="Q20" t="b">
+      <c r="Q4" t="b">
         <v>1</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>5
 3 9 2 7 5</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>3
 -1 -5 -3</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>1
 42</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>2
 0 0</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>4
 10 20 30 40</t>
         </is>
       </c>
-      <c r="AA20" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>6
 -5 -1 -9 -3 -2 -8</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="AD20" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>3
 100 5 3</t>
         </is>
       </c>
-      <c r="AE20" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AG20" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>n = int(input())
 nums = list(map(int, input().split()))
@@ -3765,13 +4984,13 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Python - Character Frequency</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>A text tool counts how many times a specific character appears. Read a line of text, then a single character, and print how many times that character occurs in the text.
 ### Input Format
@@ -3781,136 +5000,148 @@
 ```
 3
 ```
+### Example Walkthrough
+In the sample, the text is `banana` and the target character is `a`. The letter `a` appears `3` times, so the program prints `3`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="D5" t="n">
         <v>5</v>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>loops</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>for-loops</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>loops-and-iteration</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>sequence-iteration</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O21" t="b">
+      <c r="O5" t="b">
         <v>0</v>
       </c>
-      <c r="P21" t="b">
+      <c r="P5" t="b">
         <v>1</v>
       </c>
-      <c r="Q21" t="b">
+      <c r="Q5" t="b">
         <v>1</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>banana
 a</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>mississippi
 s</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>hello
 z</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>a
 a</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>aaaaaa
 a</t>
         </is>
       </c>
-      <c r="AA21" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>programming
 g</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AD21" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>Testing
 T</t>
         </is>
       </c>
-      <c r="AE21" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AG21" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>text = input()
 target = input()
@@ -3922,139 +5153,151 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Python - Fibonacci Terms</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Print the first N terms of the Fibonacci sequence (starting 0, 1) on a single line, separated by spaces.
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Print the first `N` terms of the Fibonacci sequence (starting `0`, `1`) on a single line, separated by spaces.
 ### Input Format
 - Line 1: N, the number of terms
 ### Output Format
 ```
 0 1 1 2 3
 ```
+### Example Walkthrough
+In the sample, `N` is `5`. The first five terms of the sequence are `0, 1, 1, 2, 3`, so the program prints `0 1 1 2 3`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D22" t="n">
+      <c r="D6" t="n">
         <v>5</v>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>loops</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>for-loops</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>loops-and-iteration</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>common-loop-patterns</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O22" t="b">
+      <c r="O6" t="b">
         <v>0</v>
       </c>
-      <c r="P22" t="b">
+      <c r="P6" t="b">
         <v>1</v>
       </c>
-      <c r="Q22" t="b">
+      <c r="Q6" t="b">
         <v>1</v>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>0 1 1 2 3</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>0 1 1 2 3 5 8 13</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA22" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>0 1</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>0 1 1 2 3 5 8 13 21 34 55 89</t>
         </is>
       </c>
-      <c r="AD22" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AE22" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>0 1 1 2 3 5 8 13 21 34</t>
         </is>
       </c>
-      <c r="AG22" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>n = int(input())
 a, b = 0, 1
@@ -4066,13 +5309,13 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Python - Reverse a Number</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Read a whole number and print it with its digits reversed (drop any leading zeros that result).
 ### Input Format
@@ -4081,129 +5324,141 @@
 ```
 4321
 ```
+### Example Walkthrough
+In the sample, the number is `1234`. Reversing its digits gives `4321`, so the program prints `4321`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="D7" t="n">
         <v>5</v>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>loops</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>loops-and-iteration</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>while-loops</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O23" t="b">
+      <c r="O7" t="b">
         <v>0</v>
       </c>
-      <c r="P23" t="b">
+      <c r="P7" t="b">
         <v>1</v>
       </c>
-      <c r="Q23" t="b">
+      <c r="Q7" t="b">
         <v>1</v>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>1234</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>4321</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y23" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>-89</t>
         </is>
       </c>
-      <c r="AA23" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>-98</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>987654</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>456789</t>
         </is>
       </c>
-      <c r="AD23" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="AE23" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AG23" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>n = int(input())
 sign = -1 if n &lt; 0 else 1
@@ -4216,15 +5471,15 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Python - Multiplication Grid</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Print an N by N grid where the cell in row i, column j holds i x j. Separate values in a row with single spaces.
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Print an `N` by `N` grid where the cell in row `i`, column `j` holds `i x j`. Separate values in a row with single spaces.
 ### Input Format
 - Line 1: N
 ### Output Format
@@ -4233,87 +5488,99 @@
 2 4 6
 3 6 9
 ```
+### Example Walkthrough
+In the sample, `N` is `3`. Row `1` holds `1 2 3`, row `2` holds `2 4 6`, and row `3` holds `3 6 9`, each value being the row number times the column number.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D24" t="n">
+      <c r="D8" t="n">
         <v>5</v>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>loops</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>loops-and-iteration</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>nested-loops</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O24" t="b">
+      <c r="O8" t="b">
         <v>0</v>
       </c>
-      <c r="P24" t="b">
+      <c r="P8" t="b">
         <v>1</v>
       </c>
-      <c r="Q24" t="b">
+      <c r="Q8" t="b">
         <v>1</v>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>1 2 3
 2 4 6
 3 6 9</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>1 2
 2 4</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>1 2 3 4
 2 4 6 8
@@ -4321,27 +5588,27 @@
 4 8 12 16</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y24" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6
 2 4 6 8 10 12
@@ -4351,12 +5618,12 @@
 6 12 18 24 30 36</t>
         </is>
       </c>
-      <c r="AD24" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AE24" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>1 2 3 4 5
 2 4 6 8 10
@@ -4365,7 +5632,7 @@
 5 10 15 20 25</t>
         </is>
       </c>
-      <c r="AG24" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>n = int(input())
 for i in range(1, n + 1):
@@ -4376,144 +5643,823 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Python - First Negative Stop</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for First Negative Stop. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Integers
+### Output Format
+```
+3
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>loops-and-iteration</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>loop-control-statements</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O9" t="b">
+        <v>0</v>
+      </c>
+      <c r="P9" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="b">
+        <v>1</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>1 2 -1 5</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>5 5 5</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>-1 2 3</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>0 -2</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10 -5 10</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>3 4 5 -9</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>1 0 2</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>total=0
+for x in map(int,input().split()):
+ if x&lt;0: break
+ total+=x
+print(total)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Python - Find Minimum</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Find Minimum. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Integers
+### Output Format
+```
+1
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>loops-and-iteration</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>common-loop-patterns</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>1</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>3 1 4</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0 -1 2</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>100 50 25</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>7 7 7</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>-5 -9 -1</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>-9</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>10 9 8 7</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>nums=list(map(int,input().split()))
+b=nums[0]
+for x in nums:
+ if x&lt;b: b=x
+print(b)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Python - Number Triangle</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Number Triangle. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: N
+### Output Format
+```
+1
+1 2
+1 2 3
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>loops-and-iteration</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>nested-loops</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>1</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>1
+1 2
+1 2 3</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>1
+1 2
+1 2 3
+1 2 3 4</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>1
+1 2
+1 2 3
+1 2 3 4
+1 2 3 4 5</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>1
+1 2</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>1
+1 2
+1 2 3
+1 2 3 4
+1 2 3 4 5
+1 2 3 4 5 6</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>n=int(input())
+for i in range(1,n+1): print(*range(1,i+1))</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AH11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>explanation</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>difficulty</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>bloomTaxonomy</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>subjects</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>topics</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>subTopics</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>companies</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>codingType</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>supportAllLanguages</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>enablePartialScore</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ignoreCase</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>testcase1_input</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>testcase1_output</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>testcase2_input</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>testcase2_output</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>testcase3_input</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>testcase3_output</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>testcase4_input</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>testcase4_output</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>testcase5_input</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>testcase5_output</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>testcase6_input</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>testcase6_output</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>testcase7_input</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>testcase7_output</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>preloadCode_python</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>solution_python</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>hints</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Python - Count the Primes</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Read N and print how many prime numbers there are from 2 up to and including N.
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Read `N` and print how many prime numbers there are from 2 up to and including `N`.
 ### Input Format
 - Line 1: N
 ### Output Format
 ```
 4
 ```
+### Example Walkthrough
+In the sample, `N` is `10`. The primes from `2` to `10` are `2, 3, 5, 7` - four in total - so the program prints `4`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D25" t="n">
+      <c r="D2" t="n">
         <v>5</v>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>loops</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>loops-and-iteration</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>nested-loops</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O25" t="b">
+      <c r="O2" t="b">
         <v>0</v>
       </c>
-      <c r="P25" t="b">
+      <c r="P2" t="b">
         <v>1</v>
       </c>
-      <c r="Q25" t="b">
+      <c r="Q2" t="b">
         <v>1</v>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="W25" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y25" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA25" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="AD25" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="AE25" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AG25" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>n = int(input())
 count = 0
@@ -4529,15 +6475,15 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Python - Pairs That Add Up</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Read N, a line of N numbers, and a target. Count how many pairs of positions (i before j) have values that add up to the target.
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Read `N`, a line of `N` numbers, and a target. Count how many pairs of positions (`i` before `j`) have values that add up to the target.
 ### Input Format
 - Line 1: N
 - Line 2: N space-separated numbers
@@ -4546,143 +6492,155 @@
 ```
 2
 ```
+### Example Walkthrough
+In the sample, `N` is `5` with numbers `1 2 3 4 5` and a target of `6`. The pairs `(1, 5)` and `(2, 4)` both add up to `6` - two pairs in total - so the program prints `2`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="D3" t="n">
         <v>5</v>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>loops</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>loops-and-iteration</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>nested-loops</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O26" t="b">
+      <c r="O3" t="b">
         <v>0</v>
       </c>
-      <c r="P26" t="b">
+      <c r="P3" t="b">
         <v>1</v>
       </c>
-      <c r="Q26" t="b">
+      <c r="Q3" t="b">
         <v>1</v>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>4
 1 2 3 4
 5</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>3
 1 1 1
 2</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>3
 5 6 7
 100</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>1
 5
 5</t>
         </is>
       </c>
-      <c r="Y26" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>2
 0 0
 0</t>
         </is>
       </c>
-      <c r="AA26" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>6
 1 2 3 4 5 6
 7</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD26" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>5
 -1 -2 3 4 5
 2</t>
         </is>
       </c>
-      <c r="AE26" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AG26" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>n = int(input())
 nums = list(map(int, input().split()))
@@ -4696,15 +6654,15 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Python - Row Totals</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Read a grid with R rows and C columns, then print the sum of each row on its own line, top to bottom.
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Read a grid with `R` rows and `C` columns, then print the sum of each row on its own line, top to bottom.
 ### Input Format
 - Line 1: R and C separated by a space
 - Next R lines: C space-separated numbers each
@@ -4713,83 +6671,95 @@
 6
 15
 ```
+### Example Walkthrough
+In the sample, the grid is `2` rows by `3` columns: `1 2 3` and `4 5 6`. The first row sums to `6` and the second sums to `15`, so the program prints `6` then `15`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D27" t="n">
+      <c r="D4" t="n">
         <v>5</v>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>loops</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>nested-loops</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>loops-and-iteration</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>common-loop-patterns</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O27" t="b">
+      <c r="O4" t="b">
         <v>0</v>
       </c>
-      <c r="P27" t="b">
+      <c r="P4" t="b">
         <v>1</v>
       </c>
-      <c r="Q27" t="b">
+      <c r="Q4" t="b">
         <v>1</v>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>2 3
 1 2 3
 4 5 6</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>6
 15</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>1 1
 99</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>99</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>3 2
 1 1
@@ -4797,38 +6767,38 @@
 3 3</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>2
 4
 6</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>1 1
 0</t>
         </is>
       </c>
-      <c r="Y27" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>2 2
 -1 -2
 -3 -4</t>
         </is>
       </c>
-      <c r="AA27" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>-3
 -7</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>4 1
 5
@@ -4837,7 +6807,7 @@
 20</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>5
 10
@@ -4845,7 +6815,7 @@
 20</t>
         </is>
       </c>
-      <c r="AD27" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>3 3
 1 2 3
@@ -4853,14 +6823,14 @@
 7 8 9</t>
         </is>
       </c>
-      <c r="AE27" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>6
 15
 24</t>
         </is>
       </c>
-      <c r="AG27" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>r, c = map(int, input().split())
 for _ in range(r):
@@ -4869,15 +6839,15 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Python - Inverted Star Triangle</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Print an inverted triangle of stars with N rows: the first row has N stars and each row below has one fewer, down to a single star.
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Print an inverted triangle of stars with `N` rows: the first row has `N` stars and each row below has one fewer, down to a single star.
 ### Input Format
 - Line 1: N
 ### Output Format
@@ -4887,64 +6857,76 @@
 **
 *
 ```
+### Example Walkthrough
+In the sample, `N` is `4`. The rows have `4`, `3`, `2`, and `1` stars, printing `****`, `***`, `**`, and `*` in that order.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D28" t="n">
+      <c r="D5" t="n">
         <v>5</v>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>loops</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>nested-loops</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>loops-and-iteration</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>for-loops-and-range</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O28" t="b">
+      <c r="O5" t="b">
         <v>0</v>
       </c>
-      <c r="P28" t="b">
+      <c r="P5" t="b">
         <v>1</v>
       </c>
-      <c r="Q28" t="b">
+      <c r="Q5" t="b">
         <v>1</v>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>****
 ***
@@ -4952,50 +6934,50 @@
 *</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>*</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>***
 **
 *</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Y28" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>**
 *</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>*******
 ******
@@ -5006,12 +6988,12 @@
 *</t>
         </is>
       </c>
-      <c r="AD28" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AE28" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>******
 *****
@@ -5021,7 +7003,7 @@
 *</t>
         </is>
       </c>
-      <c r="AG28" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>n = int(input())
 for i in range(n, 0, -1):
@@ -5029,15 +7011,15 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Python - Student Averages</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Read N and M, then N lines each holding M marks. For each student print their average mark rounded to 2 decimal places, one per line.
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Read `N` and `M`, then `N` lines each holding `M` marks. For each student print their average mark rounded to 2 decimal places, one per line.
 ### Input Format
 - Line 1: N (students) and M (subjects), space-separated
 - Next N lines: M space-separated marks each
@@ -5046,107 +7028,119 @@
 90.0
 70.0
 ```
+### Example Walkthrough
+In the sample, `N` is `2` and `M` is `2`. The first student's marks are `90 90`, averaging to `90.0`, and the second student's marks are `70 70`, averaging to `70.0`, so the program prints `90.0` then `70.0`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D6" t="n">
         <v>5</v>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>loops</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>nested-loops</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>loops-and-iteration</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>common-loop-patterns</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O29" t="b">
+      <c r="O6" t="b">
         <v>0</v>
       </c>
-      <c r="P29" t="b">
+      <c r="P6" t="b">
         <v>1</v>
       </c>
-      <c r="Q29" t="b">
+      <c r="Q6" t="b">
         <v>1</v>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>2 3
 80 90 100
 60 70 80</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>90.0
 70.0</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>1 2
 50 75</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>62.5</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>2 2
 100 100
 0 0</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>100.0
 0.0</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>1 1
 0</t>
         </is>
       </c>
-      <c r="Y29" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>3 2
 10 20
@@ -5154,25 +7148,25 @@
 50 60</t>
         </is>
       </c>
-      <c r="AA29" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>15.0
 35.0
 55.0</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>1 4
 90 80 70 60</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>75.0</t>
         </is>
       </c>
-      <c r="AD29" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>4 3
 1 2 3
@@ -5181,7 +7175,7 @@
 10 11 12</t>
         </is>
       </c>
-      <c r="AE29" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>2.0
 5.0
@@ -5189,7 +7183,7 @@
 11.0</t>
         </is>
       </c>
-      <c r="AG29" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>n, m = map(int, input().split())
 for _ in range(n):
@@ -5198,15 +7192,15 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Python - Repeated Digit Triangle</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Print a triangle with N rows where row i shows the digit i repeated i times (for example row 3 is '333'). N is at most 9.
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Print a triangle with `N` rows where row `i` shows the digit `i` repeated `i` times (for example row 3 is `333`). `N` is at most 9.
 ### Input Format
 - Line 1: N (1 to 9)
 ### Output Format
@@ -5215,86 +7209,98 @@
 22
 333
 ```
+### Example Walkthrough
+In the sample, `N` is `3`. Row `1` is `1`, row `2` is `22`, and row `3` is `333`, each digit repeated as many times as its row number.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D30" t="n">
+      <c r="D7" t="n">
         <v>5</v>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>loops</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>nested-loops</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>loops-and-iteration</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>for-loops-and-range</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O30" t="b">
+      <c r="O7" t="b">
         <v>0</v>
       </c>
-      <c r="P30" t="b">
+      <c r="P7" t="b">
         <v>1</v>
       </c>
-      <c r="Q30" t="b">
+      <c r="Q7" t="b">
         <v>1</v>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>1
 22
 333</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>1
 22
@@ -5303,23 +7309,23 @@
 55555</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Y30" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>1
 22</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AA30" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>1
 22
@@ -5332,12 +7338,12 @@
 999999999</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1
 22
@@ -5348,12 +7354,12 @@
 7777777</t>
         </is>
       </c>
-      <c r="AD30" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AE30" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>1
 22
@@ -5361,7 +7367,7 @@
 4444</t>
         </is>
       </c>
-      <c r="AG30" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>n = int(input())
 for i in range(1, n + 1):
@@ -5369,15 +7375,15 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Python - Biggest in the Grid</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Read a grid with R rows and C columns and print the single largest value found anywhere in the grid.
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Read a grid with `R` rows and `C` columns and print the single largest value found anywhere in the grid.
 ### Input Format
 - Line 1: R and C separated by a space
 - Next R lines: C space-separated numbers each
@@ -5385,105 +7391,117 @@
 ```
 9
 ```
+### Example Walkthrough
+In the sample, the grid is `2` rows by `2` columns: `3 9` and `5 1`. The largest value anywhere in the grid is `9`, so the program prints `9`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D31" t="n">
+      <c r="D8" t="n">
         <v>5</v>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>loops</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>loops-and-iteration</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>nested-loops</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O31" t="b">
+      <c r="O8" t="b">
         <v>0</v>
       </c>
-      <c r="P31" t="b">
+      <c r="P8" t="b">
         <v>1</v>
       </c>
-      <c r="Q31" t="b">
+      <c r="Q8" t="b">
         <v>1</v>
       </c>
-      <c r="R31" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>2 3
 1 5 3
 9 2 4</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>1 1
 7</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>2 2
 -1 -2
 -3 -4</t>
         </is>
       </c>
-      <c r="W31" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>1 1
 0</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>3 3
 1 2 3
@@ -5491,23 +7509,23 @@
 7 8 9</t>
         </is>
       </c>
-      <c r="AA31" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>1 4
 10 20 30 40</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="AD31" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>4 1
 -5
@@ -5516,12 +7534,12 @@
 -20</t>
         </is>
       </c>
-      <c r="AE31" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="AG31" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>r, c = map(int, input().split())
 best = None
@@ -5534,6 +7552,503 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Python - Prime Range Count</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Prime Range Count. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: N
+### Output Format
+```
+4
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>loops-and-iteration</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>nested-loops</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O9" t="b">
+        <v>0</v>
+      </c>
+      <c r="P9" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="b">
+        <v>1</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>n=int(input())
+c=0
+for x in range(2,n+1):
+ p=True
+ for d in range(2,x):
+  if x%d==0: p=False; break
+ if p: c+=1
+print(c)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Python - Grid Border Stars</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Grid Border Stars. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: N
+### Output Format
+```
+***
+*.*
+***
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>loops-and-iteration</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>nested-loops</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>1</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>***
+*.*
+***</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>****
+*..*
+*..*
+****</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>*****
+*...*
+*...*
+*...*
+*****</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>**
+**</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>******
+*....*
+*....*
+*....*
+*....*
+******</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>*******
+*.....*
+*.....*
+*.....*
+*.....*
+*.....*
+*******</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>n=int(input())
+for r in range(n):
+ row=""
+ for c in range(n): row += "*" if r==0 or c==0 or r==n-1 or c==n-1 else "."
+ print(row)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Python - Digit Product</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Digit Product. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Number
+### Output Format
+```
+6
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>loops-and-iteration</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>while-loops</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>1</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>729</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>1111</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>808</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>n=int(input())
+prod=0 if n==0 else 1
+while n&gt;0:
+ prod*=n%10; n//=10
+print(prod)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/content/Question Bank/Coding Questions/Unit 4 - Looping/Unit 4 - Looping - Coding Questions.xlsx
+++ b/content/Question Bank/Coding Questions/Unit 4 - Looping/Unit 4 - Looping - Coding Questions.xlsx
@@ -2116,16 +2116,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Sum First N. Read the input values and print the required result exactly.
+          <t>A community fundraiser sells raffle tickets numbered 1, 2, 3, and so on. At the end of the day, the volunteer wants to know the total of every ticket number sold, from ticket 1 up to the last ticket, `N`.
+Write a program that reads a whole number `N` and prints the sum of every whole number from 1 to `N` (inclusive). If `N` is 0, there are no tickets to add, so the sum is 0.
 ### Input Format
 - Line 1: N
 ### Output Format
 ```
 15
 ```
+### Example Walkthrough
+In the sample, `N` is 5. Adding every whole number from 1 through 5 gives `1 + 2 + 3 + 4 + 5 = 15`, so the program prints `15`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- All numeric inputs are valid numbers in the ranges implied by the examples.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -2272,7 +2275,8 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Print Countdown. Read the input values and print the required result exactly.
+          <t>A microwave display flashes the remaining seconds one at a time before the timer goes off. Given a starting number of seconds `N`, the display must show every second from `N` down to 1, one value per line, and then stop.
+Write a program that reads a whole number `N` and prints every whole number from `N` down to 1, one number per line. If `N` is 0 (or less), the timer has already finished, so nothing is printed.
 ### Input Format
 - Line 1: N
 ### Output Format
@@ -2281,9 +2285,11 @@
 2
 1
 ```
+### Example Walkthrough
+In the sample, `N` is 3. The display starts at 3 and prints it, then counts down one step at a time - printing `2`, then `1` - and stops once it reaches 1. That gives three lines in decreasing order.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- All numeric inputs are valid numbers in the ranges implied by the examples.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -2384,7 +2390,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr">
         <is>
           <t>7</t>
@@ -3988,16 +3993,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Count Letter A. Read the input values and print the required result exactly.
+          <t>A teacher is running a spelling game and wants to know how often the lowercase letter `a` appears in a student's word.
+Write a program that reads a line of text and counts how many times the lowercase letter `a` appears in it, then prints that count. Uppercase `A` is not counted.
 ### Input Format
 - Line 1: Text
 ### Output Format
 ```
 3
 ```
+### Example Walkthrough
+In the sample, the text is `banana`. Scanning each character, the letter `a` appears three times - so the program prints `3`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- The text contains only letters, with no spaces.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -4145,16 +4153,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Multiples List. Read the input values and print the required result exactly.
+          <t>A multiplication drill app shows students the first five multiples of a chosen number `N`, to help them memorize their tables.
+Write a program that reads a whole number `N` and prints the first five multiples of `N` (that is, `N*1, N*2, N*3, N*4, N*5`), separated by single spaces on one line.
 ### Input Format
 - Line 1: N
 ### Output Format
 ```
 2 4 6 8 10
 ```
+### Example Walkthrough
+In the sample, `N` is 2. The first five multiples of 2 are `2, 4, 6, 8, 10`, so the program prints `2 4 6 8 10` on one line, separated by spaces.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- All numeric inputs are valid numbers in the ranges implied by the examples, including zero and negative values.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -5651,16 +5662,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for First Negative Stop. Read the input values and print the required result exactly.
+          <t>A fuel gauge logs a stream of readings, but the sensor sends a negative value whenever it malfunctions. The system must add up the readings as they come in, but stop the moment it sees a negative value - the faulty reading and everything after it should be ignored.
+Write a program that reads a line of space-separated integers and adds them up one at a time, stopping as soon as it encounters a negative number (that negative number itself is not added, and nothing after it is read). Print the total accumulated before the first negative number appears.
 ### Input Format
-- Line 1: Integers
+- Line 1: Space-separated integers
 ### Output Format
 ```
 3
 ```
+### Example Walkthrough
+In the sample, the integers are `1 2 -1 5`. The program adds `1`, then `2`, giving a running total of `3`. It then reaches `-1`, which is negative, so it stops immediately - the `5` after it is never added. The program prints `3`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- The line contains at least one integer.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -5808,16 +5822,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Find Minimum. Read the input values and print the required result exactly.
+          <t>A weather station logs several temperature readings taken during the day, and the analyst wants to know the lowest reading recorded.
+Write a program that reads a line of space-separated integers and prints the smallest value among them.
 ### Input Format
-- Line 1: Integers
+- Line 1: Space-separated integers
 ### Output Format
 ```
 1
 ```
+### Example Walkthrough
+In the sample, the integers are `3 1 4`. Comparing them one at a time, `1` is smaller than `3`, and `4` is not smaller than `1`, so the smallest value overall is `1`, which the program prints.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- The line contains at least one integer.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -5965,7 +5982,8 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Number Triangle. Read the input values and print the required result exactly.
+          <t>A print shop is designing a staircase-shaped poster made entirely of numbers, where each row is one number longer than the row before it.
+Write a program that reads a whole number `N` and prints `N` rows: row `i` (starting from row 1) contains the numbers from `1` to `i`, separated by single spaces. If `N` is 0, print nothing.
 ### Input Format
 - Line 1: N
 ### Output Format
@@ -5974,9 +5992,11 @@
 1 2
 1 2 3
 ```
+### Example Walkthrough
+In the sample, `N` is 3. Row 1 prints just `1`. Row 2 prints `1 2`. Row 3 prints `1 2 3`. That gives the three lines shown above, each one number longer than the last.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- All numeric inputs are valid numbers in the ranges implied by the examples.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -6076,7 +6096,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr">
         <is>
           <t>5</t>
@@ -7560,16 +7579,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Prime Range Count. Read the input values and print the required result exactly.
+          <t>A locker room assigns lockers numbered from 2 up to `N`, and the facility manager wants to know how many of those locker numbers are prime, since prime-numbered lockers get a special security tag.
+Write a program that reads a whole number `N` and counts how many prime numbers exist from 2 up to and including `N` (a number is prime if it has no divisors other than 1 and itself), then prints that count.
 ### Input Format
 - Line 1: N
 ### Output Format
 ```
 4
 ```
+### Example Walkthrough
+In the sample, `N` is 10. The prime numbers from 2 to 10 are `2, 3, 5, 7` - four in total - so the program prints `4`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- All numeric inputs are valid numbers in the ranges implied by the examples.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -7720,7 +7742,8 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Grid Border Stars. Read the input values and print the required result exactly.
+          <t>A gardener is fencing a square plot and wants a quick sketch of the layout: the outer fence marked with stars and the open ground inside marked with dots.
+Write a program that reads a whole number `N` and prints an `N x N` grid. Every cell on the outer border (the first row, the last row, the first column, or the last column) is printed as `*`, and every other cell is printed as `.`, with each row on its own line.
 ### Input Format
 - Line 1: N
 ### Output Format
@@ -7729,9 +7752,11 @@
 *.*
 ***
 ```
+### Example Walkthrough
+In the sample, `N` is 3. The grid has 3 rows and 3 columns. Every cell lies on the border except the very center cell, so the first and last rows are all stars (`***`), and the middle row has a star, a dot, and a star (`*.*`).
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- All numeric inputs are valid numbers in the ranges implied by the examples.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -7900,16 +7925,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Digit Product. Read the input values and print the required result exactly.
+          <t>A simple PIN-strength checker multiplies together all the digits of a code to produce a single check value; if any digit is 0, the check value collapses to 0, flagging a weak PIN.
+Write a program that reads a whole number `N` and prints the product of all of its digits. If `N` is 0, print 0.
 ### Input Format
-- Line 1: Number
+- Line 1: N
 ### Output Format
 ```
 6
 ```
+### Example Walkthrough
+In the sample, `N` is 123. Its digits are `1`, `2`, and `3`. Multiplying them together gives `1 * 2 * 3 = 6`, so the program prints `6`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- All numeric inputs are valid numbers in the ranges implied by the examples.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D11" t="n">

--- a/content/Question Bank/Coding Questions/Unit 4 - Looping/Unit 4 - Looping - Coding Questions.xlsx
+++ b/content/Question Bank/Coding Questions/Unit 4 - Looping/Unit 4 - Looping - Coding Questions.xlsx
@@ -2116,8 +2116,8 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A community fundraiser sells raffle tickets numbered 1, 2, 3, and so on. At the end of the day, the volunteer wants to know the total of every ticket number sold, from ticket 1 up to the last ticket, `N`.
-Write a program that reads a whole number `N` and prints the sum of every whole number from 1 to `N` (inclusive). If `N` is 0, there are no tickets to add, so the sum is 0.
+          <t>A summer camp gives out participation stars in order: the first camper to sign up gets 1 star, the second gets 2, the third gets 3, and so on up to the Nth camper. The instructor wants the total number of stars given out without adding them up by hand.
+Write a program that reads a whole number N and prints the sum of all whole numbers from 1 to N using a loop.
 ### Input Format
 - Line 1: N
 ### Output Format
@@ -2125,9 +2125,9 @@
 15
 ```
 ### Example Walkthrough
-In the sample, `N` is 5. Adding every whole number from 1 through 5 gives `1 + 2 + 3 + 4 + 5 = 15`, so the program prints `15`.
+In the sample, N is 5. The loop adds 1 + 2 + 3 + 4 + 5, which totals 15, so the program prints `15`.
 ### Constraints
-- All numeric inputs are valid numbers in the ranges implied by the examples.
+- All numeric inputs are valid whole numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
@@ -2275,8 +2275,8 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A microwave display flashes the remaining seconds one at a time before the timer goes off. Given a starting number of seconds `N`, the display must show every second from `N` down to 1, one value per line, and then stop.
-Write a program that reads a whole number `N` and prints every whole number from `N` down to 1, one number per line. If `N` is 0 (or less), the timer has already finished, so nothing is printed.
+          <t>An elevator display in a busy office building shows a warning countdown before the doors close, ticking down one second at a time from however many seconds are left until it reaches 1. If 0 seconds are configured, nothing is displayed at all.
+Write a program that reads a whole number N and uses a loop to print every whole number from N down to 1, one number per line. If N is 0 or less, print nothing.
 ### Input Format
 - Line 1: N
 ### Output Format
@@ -2286,9 +2286,9 @@
 1
 ```
 ### Example Walkthrough
-In the sample, `N` is 3. The display starts at 3 and prints it, then counts down one step at a time - printing `2`, then `1` - and stops once it reaches 1. That gives three lines in decreasing order.
+In the sample, N is 3. The loop starts at 3 and prints it, then steps down to 2, then 1, giving three lines in decreasing order.
 ### Constraints
-- All numeric inputs are valid numbers in the ranges implied by the examples.
+- All numeric inputs are valid whole numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
@@ -3993,18 +3993,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A teacher is running a spelling game and wants to know how often the lowercase letter `a` appears in a student's word.
-Write a program that reads a line of text and counts how many times the lowercase letter `a` appears in it, then prints that count. Uppercase `A` is not counted.
+          <t>A word game show counts how many times the lowercase letter `a` appears in the word a contestant submits, since that is how many bonus points they earn. A capital `A` does not count as a match.
+Write a program that reads a line of text and prints how many times the lowercase letter `a` appears in it, scanning the text one character at a time with a loop.
 ### Input Format
-- Line 1: Text
+- Line 1: A line of text
 ### Output Format
 ```
 3
 ```
 ### Example Walkthrough
-In the sample, the text is `banana`. Scanning each character, the letter `a` appears three times - so the program prints `3`.
+In the sample, the text is `banana`. Scanning letter by letter, the lowercase `a` appears at positions 2, 4, and 6, which is 3 times, so the program prints `3`.
 ### Constraints
-- The text contains only letters, with no spaces.
+- The input is a valid line of text with no leading or trailing spaces.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
@@ -4153,8 +4153,8 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A multiplication drill app shows students the first five multiples of a chosen number `N`, to help them memorize their tables.
-Write a program that reads a whole number `N` and prints the first five multiples of `N` (that is, `N*1, N*2, N*3, N*4, N*5`), separated by single spaces on one line.
+          <t>A bus company wants a quick preview of the next 5 departure times once a route's interval is set: if buses run every N minutes, departures happen at N, 2N, 3N, 4N, and 5N minutes from now.
+Write a program that reads a whole number N and prints the first 5 multiples of N, separated by single spaces, on one line.
 ### Input Format
 - Line 1: N
 ### Output Format
@@ -4162,9 +4162,9 @@
 2 4 6 8 10
 ```
 ### Example Walkthrough
-In the sample, `N` is 2. The first five multiples of 2 are `2, 4, 6, 8, 10`, so the program prints `2 4 6 8 10` on one line, separated by spaces.
+In the sample, N is 2. The first 5 multiples of 2 are 2, 4, 6, 8, and 10, so the program prints `2 4 6 8 10`.
 ### Constraints
-- All numeric inputs are valid numbers in the ranges implied by the examples, including zero and negative values.
+- All numeric inputs are valid whole numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
@@ -5662,18 +5662,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A fuel gauge logs a stream of readings, but the sensor sends a negative value whenever it malfunctions. The system must add up the readings as they come in, but stop the moment it sees a negative value - the faulty reading and everything after it should be ignored.
-Write a program that reads a line of space-separated integers and adds them up one at a time, stopping as soon as it encounters a negative number (that negative number itself is not added, and nothing after it is read). Print the total accumulated before the first negative number appears.
+          <t>A vending machine adds up the value of coins as they are inserted one by one, but stops counting the instant its sensor reports an invalid (negative) reading, without adding that faulty reading to the total.
+Write a program that reads a line of whole numbers separated by spaces and adds them up one at a time using a loop, stopping (without adding it) as soon as a negative number is seen. Print the total collected so far.
 ### Input Format
-- Line 1: Space-separated integers
+- Line 1: Whole numbers separated by spaces
 ### Output Format
 ```
 3
 ```
 ### Example Walkthrough
-In the sample, the integers are `1 2 -1 5`. The program adds `1`, then `2`, giving a running total of `3`. It then reaches `-1`, which is negative, so it stops immediately - the `5` after it is never added. The program prints `3`.
+In the sample, the numbers are `1 2 -1 5`. The loop adds 1, then 2, reaching a total of 3, then sees -1 and stops immediately without adding it or looking at the remaining 5. The program prints `3`.
 ### Constraints
-- The line contains at least one integer.
+- All numeric inputs are valid whole numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
@@ -5822,18 +5822,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A weather station logs several temperature readings taken during the day, and the analyst wants to know the lowest reading recorded.
-Write a program that reads a line of space-separated integers and prints the smallest value among them.
+          <t>A weather app scans a list of temperature readings taken through the day and reports the lowest one, so the evening news can announce the day's coldest moment.
+Write a program that reads a line of whole numbers separated by spaces and prints the smallest one, found using a loop that compares each value to the smallest seen so far.
 ### Input Format
-- Line 1: Space-separated integers
+- Line 1: Whole numbers separated by spaces
 ### Output Format
 ```
 1
 ```
 ### Example Walkthrough
-In the sample, the integers are `3 1 4`. Comparing them one at a time, `1` is smaller than `3`, and `4` is not smaller than `1`, so the smallest value overall is `1`, which the program prints.
+In the sample, the numbers are `3 1 4`. Starting with 3 as the smallest seen so far, the loop compares it to 1 (smaller, so 1 becomes the smallest) and then to 4 (not smaller), leaving 1 as the overall minimum. The program prints `1`.
 ### Constraints
-- The line contains at least one integer.
+- All numeric inputs are valid whole numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
@@ -5982,8 +5982,8 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A print shop is designing a staircase-shaped poster made entirely of numbers, where each row is one number longer than the row before it.
-Write a program that reads a whole number `N` and prints `N` rows: row `i` (starting from row 1) contains the numbers from `1` to `i`, separated by single spaces. If `N` is 0, print nothing.
+          <t>A lecture hall's seating-chart generator prints an increasing triangle of numbers to show students how seats fill up row by row: row 1 shows just seat 1, row 2 shows seats 1 and 2, and so on up to row N.
+Write a program that reads a whole number N and, using nested loops, prints N rows where row `i` contains the numbers from 1 to `i` separated by single spaces, each row on its own line.
 ### Input Format
 - Line 1: N
 ### Output Format
@@ -5993,9 +5993,9 @@
 1 2 3
 ```
 ### Example Walkthrough
-In the sample, `N` is 3. Row 1 prints just `1`. Row 2 prints `1 2`. Row 3 prints `1 2 3`. That gives the three lines shown above, each one number longer than the last.
+In the sample, N is 3. The outer loop runs for rows 1 through 3: row 1 prints just `1`, row 2 prints `1 2`, and row 3 prints `1 2 3`, giving three lines that grow by one number each time.
 ### Constraints
-- All numeric inputs are valid numbers in the ranges implied by the examples.
+- All numeric inputs are valid whole numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
@@ -7579,8 +7579,8 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A locker room assigns lockers numbered from 2 up to `N`, and the facility manager wants to know how many of those locker numbers are prime, since prime-numbered lockers get a special security tag.
-Write a program that reads a whole number `N` and counts how many prime numbers exist from 2 up to and including `N` (a number is prime if it has no divisors other than 1 and itself), then prints that count.
+          <t>A number-theory quiz app reveals a fun fact after each round: how many prime numbers exist from 2 up to whatever limit N the player chose.
+Write a program that reads a whole number N and prints how many prime numbers there are from 2 up to and including N. A prime number is a whole number greater than 1 that no smaller number (except 1) divides exactly.
 ### Input Format
 - Line 1: N
 ### Output Format
@@ -7588,9 +7588,9 @@
 4
 ```
 ### Example Walkthrough
-In the sample, `N` is 10. The prime numbers from 2 to 10 are `2, 3, 5, 7` - four in total - so the program prints `4`.
+In the sample, N is 10. The prime numbers from 2 to 10 are 2, 3, 5, and 7 — four of them — so the program prints `4`.
 ### Constraints
-- All numeric inputs are valid numbers in the ranges implied by the examples.
+- All numeric inputs are valid whole numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
@@ -7742,8 +7742,8 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A gardener is fencing a square plot and wants a quick sketch of the layout: the outer fence marked with stars and the open ground inside marked with dots.
-Write a program that reads a whole number `N` and prints an `N x N` grid. Every cell on the outer border (the first row, the last row, the first column, or the last column) is printed as `*`, and every other cell is printed as `.`, with each row on its own line.
+          <t>A game designer is prototyping a square arena using text characters before building real art: the outer wall is drawn with stars and the open floor space inside is drawn with dots, on an N x N grid.
+Write a program that reads a whole number N and, using nested loops, prints an N x N grid where every cell on the outer border (first row, last row, first column, or last column) is `*` and every other cell is `.`, one row per line with no spaces between characters.
 ### Input Format
 - Line 1: N
 ### Output Format
@@ -7753,9 +7753,9 @@
 ***
 ```
 ### Example Walkthrough
-In the sample, `N` is 3. The grid has 3 rows and 3 columns. Every cell lies on the border except the very center cell, so the first and last rows are all stars (`***`), and the middle row has a star, a dot, and a star (`*.*`).
+In the sample, N is 3. Every cell in the first row, last row, first column, or last column is part of the border, so the top and bottom rows are all stars (`***`) and the middle row has stars only at its two ends (`*.*`).
 ### Constraints
-- All numeric inputs are valid numbers in the ranges implied by the examples.
+- All numeric inputs are valid whole numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
@@ -7925,18 +7925,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A simple PIN-strength checker multiplies together all the digits of a code to produce a single check value; if any digit is 0, the check value collapses to 0, flagging a weak PIN.
-Write a program that reads a whole number `N` and prints the product of all of its digits. If `N` is 0, print 0.
+          <t>A puzzle app computes a "lucky number" for each ticket by multiplying together all of its digits, so a ticket containing a 0 anywhere always ends up with a lucky number of 0.
+Write a program that reads a whole number and prints the product of its digits, found using a loop that repeatedly takes the last digit (the remainder when dividing by 10) and removes it from the number. If the number itself is 0, print `0`.
 ### Input Format
-- Line 1: N
+- Line 1: A whole number
 ### Output Format
 ```
 6
 ```
 ### Example Walkthrough
-In the sample, `N` is 123. Its digits are `1`, `2`, and `3`. Multiplying them together gives `1 * 2 * 3 = 6`, so the program prints `6`.
+In the sample, the number is 123. Its digits are 1, 2, and 3, and multiplying them gives 1 x 2 x 3 = 6, so the program prints `6`.
 ### Constraints
-- All numeric inputs are valid numbers in the ranges implied by the examples.
+- All numeric inputs are valid whole numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>

--- a/content/Question Bank/Coding Questions/Unit 4 - Looping/Unit 4 - Looping - Coding Questions.xlsx
+++ b/content/Question Bank/Coding Questions/Unit 4 - Looping/Unit 4 - Looping - Coding Questions.xlsx
@@ -7,10 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 3" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 4" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - Coding - Unit 4" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH11"/>
+  <dimension ref="A1:AH41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -601,21 +598,11 @@
         <is>
           <t>The science club is launching its model rocket at the tech fest, and the big screen must count down dramatically before lift-off. The countdown starts at whatever number the operator types in and ticks all the way down to 1.
 Write a program that reads a whole number `N` and uses a loop to print every number from `N` down to 1, one number per line.
-### Input Format
-- Line 1: N, the starting number
-### Output Format
-```
-5
-4
-3
-2
-1
-```
 ### Example Walkthrough
 In the sample, `N` is 5. The loop starts at 5 and prints it, then steps down one at a time - 4, then 3, then 2 - and stops after printing `1`. That gives five lines in decreasing order.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -772,9 +759,10 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>n = int(input())
-for i in range(n, 0, -1):
-    print(i)</t>
+          <t xml:space="preserve">n = int(input())
+for i in range(n, 0, -1):  # count down from n to 1
+    print(i)
+</t>
         </is>
       </c>
     </row>
@@ -788,17 +776,11 @@
         <is>
           <t>A spelling game at the school fest awards a point for every vowel in the word a player types. The game needs a counter that scans the word letter by letter and keeps a running total.
 Write a program that reads one line of text and prints how many vowels (`a`, `e`, `i`, `o`, `u`) it contains. Count capital and small letters alike - `A` and `a` are both vowels.
-### Input Format
-- Line 1: A line of text
-### Output Format
-```
-5
-```
 ### Example Walkthrough
 In the sample, the input is `education`. Scanning it letter by letter, the vowels found are `e`, `u`, `a`, `i`, and `o` - five in total - so the program prints `5`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -930,12 +912,13 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>text = input()
+          <t xml:space="preserve">text = input()
 count = 0
-for ch in text.lower():
+for ch in text.lower():  # lowercase so both cases are treated the same
     if ch in "aeiou":
-        count += 1
-print(count)</t>
+        count += 1      # found a vowel, add it to the running total
+print(count)
+</t>
         </is>
       </c>
     </row>
@@ -949,26 +932,11 @@
         <is>
           <t>Ravi is helping his younger sister memorise multiplication tables, and he builds a small app that prints any table on demand. She types a number, and the full table from 1 to 10 appears instantly.
 Write a program that reads a whole number `N` and prints its multiplication table from 1 to 10, one line per product, in the exact form `N x i = value` with single spaces around the `x` and the `=`.
-### Input Format
-- Line 1: N, the number
-### Output Format
-```
-2 x 1 = 2
-2 x 2 = 4
-2 x 3 = 6
-2 x 4 = 8
-2 x 5 = 10
-2 x 6 = 12
-2 x 7 = 14
-2 x 8 = 16
-2 x 9 = 18
-2 x 10 = 20
-```
 ### Example Walkthrough
 In the sample, `N` is 2. The loop runs `i` from 1 to 10, printing `2 x 1 = 2` first, then `2 x 2 = 4`, and so on, ending with `2 x 10 = 20` - ten lines in all.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -1163,9 +1131,10 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>n = int(input())
-for i in range(1, 11):
-    print(n, "x", i, "=", n * i)</t>
+          <t xml:space="preserve">n = int(input())
+for i in range(1, 11):  # multiplier runs from 1 through 10
+    print(n, "x", i, "=", n * i)
+</t>
         </is>
       </c>
     </row>
@@ -1179,17 +1148,11 @@
         <is>
           <t>A form validator on a payment page needs to know how many digits a customer's number has before accepting it. The developer counts the digits the classic way: repeatedly chopping off the last digit until nothing is left, counting one chop each time.
 Write a program that reads a whole number and prints how many digits it contains.
-### Input Format
-- Line 1: A whole number
-### Output Format
-```
-5
-```
 ### Example Walkthrough
 In the sample, the number is 12345. Chopping off the last digit repeatedly gives 1234, then 123, then 12, then 1, then 0 - five chops in total - so the number has 5 digits and the program prints `5`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -1321,15 +1284,16 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>n = int(input())
-n = abs(n)
+          <t xml:space="preserve">n = int(input())
+n = abs(n)              # ignore sign, only digits matter
 count = 0
 while n &gt; 0:
-    count += 1
-    n //= 10
+    count += 1           # one more digit found
+    n //= 10             # drop the last digit
 if count == 0:
-    count = 1
-print(count)</t>
+    count = 1             # handle the case where n was 0 (still 1 digit)
+print(count)
+</t>
         </is>
       </c>
     </row>
@@ -1343,21 +1307,11 @@
         <is>
           <t>In a classic classroom counting game, players count upward from 1, but any number divisible by 3 is replaced with `Fizz`, any number divisible by 5 with `Buzz`, and any number divisible by both with `FizzBuzz`. Your job is to teach the computer to play a full round on its own.
 Write a program that reads a whole number `N` and prints the sequence from 1 to `N`, one value per line, applying the three replacement rules. Remember to check the "divisible by both" case first.
-### Input Format
-- Line 1: N
-### Output Format
-```
-1
-2
-Fizz
-4
-Buzz
-```
 ### Example Walkthrough
 In the sample, `N` is 5. The numbers 1 and 2 are printed as they are; 3 is divisible by 3, so `Fizz` appears in its place; 4 is printed normally; and 5 is divisible by 5, so the round ends with `Buzz`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -1601,16 +1555,17 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>n = int(input())
+          <t xml:space="preserve">n = int(input())
 for i in range(1, n + 1):
-    if i % 15 == 0:
+    if i % 15 == 0:        # divisible by both 3 and 5
         print("FizzBuzz")
     elif i % 3 == 0:
         print("Fizz")
     elif i % 5 == 0:
         print("Buzz")
     else:
-        print(i)</t>
+        print(i)
+</t>
         </is>
       </c>
     </row>
@@ -1624,17 +1579,11 @@
         <is>
           <t>A courier company's tracking codes end with a checksum - a small number made by adding up all the digits of the code. Before a parcel is booked, the system must work out this digit sum to verify the code.
 Write a program that reads a whole number and prints the sum of its digits. Use a loop that repeatedly takes the last digit (the remainder when dividing by 10, i.e. what is left over) and then removes that digit from the number.
-### Input Format
-- Line 1: A whole number
-### Output Format
-```
-10
-```
 ### Example Walkthrough
 In the sample, the number is 1234. Its digits are 1, 2, 3, and 4, and adding them gives 1 + 2 + 3 + 4 = 10, so the program prints `10`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1766,12 +1715,13 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>n = abs(int(input()))
+          <t xml:space="preserve">n = abs(int(input()))    # ignore sign, only digits matter
 total = 0
 while n &gt; 0:
-    total += n % 10
-    n //= 10
-print(total)</t>
+    total += n % 10       # add the last digit to the total
+    n //= 10               # drop the last digit
+print(total)
+</t>
         </is>
       </c>
     </row>
@@ -1785,18 +1735,11 @@
         <is>
           <t>For the fest decorations, Kiran has two ribbon rolls - one 12 metres long and one 18 metres long - and wants to cut both into equal pieces that are as long as possible with nothing wasted. The answer is the greatest common divisor (GCD): the largest number that divides both lengths exactly.
 Write a program that reads two whole numbers and prints their GCD using Euclid's method of repeated remainders: keep dividing and taking the remainder until the remainder becomes 0; the last non-zero value is the answer.
-### Input Format
-- Line 1: First number
-- Line 2: Second number
-### Output Format
-```
-6
-```
 ### Example Walkthrough
 In the sample, the numbers are 12 and 18. Dividing 18 by 12 leaves a remainder of 6; dividing 12 by 6 leaves a remainder of 0, so the process stops and the GCD is 6. Ribbon pieces of 6 metres use up both rolls perfectly, and the program prints `6`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1935,11 +1878,12 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>a = int(input())
+          <t xml:space="preserve">a = int(input())
 b = int(input())
-while b != 0:
+while b != 0:             # Euclid's algorithm: keep reducing until remainder is 0
     a, b = b, a % b
-print(a)</t>
+print(a)
+</t>
         </is>
       </c>
     </row>
@@ -1953,17 +1897,11 @@
         <is>
           <t>In the maths club's number game, a player shouts out a number and the club's app must instantly say whether it is prime. A prime number is a whole number greater than 1 that no smaller number (except 1) divides exactly - 7 is prime, but 8 is not, because 2 divides it.
 Write a program that reads a whole number and prints exactly `Prime` if it is a prime number, and exactly `Not Prime` otherwise. Use a loop to test the possible divisors.
-### Input Format
-- Line 1: A whole number
-### Output Format
-```
-Prime
-```
 ### Example Walkthrough
 In the sample, the number is 7. Testing the possible divisors 2, 3, 4, 5, and 6, none of them divides 7 without a remainder, so 7 is prime and the program prints `Prime`. A number like 9 would be caught by 3 and print `Not Prime`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -2095,16 +2033,17 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>n = int(input())
+          <t xml:space="preserve">n = int(input())
 if n &lt; 2:
     print("Not Prime")
 else:
     is_prime = True
-    for i in range(2, int(n ** 0.5) + 1):
+    for i in range(2, int(n ** 0.5) + 1):   # only need to check up to sqrt(n)
         if n % i == 0:
             is_prime = False
-            break
-    print("Prime" if is_prime else "Not Prime")</t>
+            break        # found a divisor, no need to check further
+    print("Prime" if is_prime else "Not Prime")
+</t>
         </is>
       </c>
     </row>
@@ -2118,17 +2057,11 @@
         <is>
           <t>A summer camp gives out participation stars in order: the first camper to sign up gets 1 star, the second gets 2, the third gets 3, and so on up to the Nth camper. The instructor wants the total number of stars given out without adding them up by hand.
 Write a program that reads a whole number N and prints the sum of all whole numbers from 1 to N using a loop.
-### Input Format
-- Line 1: N
-### Output Format
-```
-15
-```
 ### Example Walkthrough
 In the sample, N is 5. The loop adds 1 + 2 + 3 + 4 + 5, which totals 15, so the program prints `15`.
 ### Constraints
 - All numeric inputs are valid whole numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -2260,10 +2193,11 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>n=int(input())
+          <t xml:space="preserve">n=int(input())
 t=0
-for i in range(1,n+1): t+=i
-print(t)</t>
+for i in range(1,n+1): t+=i  # add each number from 1 to n
+print(t)
+</t>
         </is>
       </c>
     </row>
@@ -2277,19 +2211,11 @@
         <is>
           <t>An elevator display in a busy office building shows a warning countdown before the doors close, ticking down one second at a time from however many seconds are left until it reaches 1. If 0 seconds are configured, nothing is displayed at all.
 Write a program that reads a whole number N and uses a loop to print every whole number from N down to 1, one number per line. If N is 0 or less, print nothing.
-### Input Format
-- Line 1: N
-### Output Format
-```
-3
-2
-1
-```
 ### Example Walkthrough
 In the sample, N is 3. The loop starts at 3 and prints it, then steps down to 2, then 1, giving three lines in decreasing order.
 ### Constraints
 - All numeric inputs are valid whole numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -2432,287 +2358,93 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>n=int(input())
+          <t xml:space="preserve">n=int(input())
 while n&gt;0:
- print(n); n-=1</t>
+ print(n); n-=1  # show current count, then move one step closer to 0
+</t>
         </is>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AH11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>explanation</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>difficulty</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>bloomTaxonomy</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>tags</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>subjects</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>topics</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>subTopics</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>companies</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>codingType</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>language</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>supportAllLanguages</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>enablePartialScore</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>ignoreCase</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>testcase1_input</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>testcase1_output</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>testcase2_input</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>testcase2_output</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>testcase3_input</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>testcase3_output</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>testcase4_input</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>testcase4_output</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>testcase5_input</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>testcase5_output</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>testcase6_input</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>testcase6_output</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>testcase7_input</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>testcase7_output</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>preloadCode_python</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>solution_python</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>hints</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Python - Star Staircase</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>For the freshers' party, the decoration team is sticking star-shaped stickers on the staircase wall: one star on the top row, two on the next, and so on, growing by one star each row. They want a program that previews the pattern for any height.
 Write a program that reads a whole number `N` and prints `N` rows of stars, where row 1 has one star, row 2 has two stars, and in general row `i` has `i` stars, with no spaces in between.
-### Input Format
-- Line 1: N, the number of rows
-### Output Format
-```
-*
-**
-***
-****
-```
 ### Example Walkthrough
 In the sample, `N` is 4. The loop prints one star on the first line, two on the second, three on the third, and four on the fourth, producing a staircase that grows by exactly one star per row.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
         <v>5</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>loops-and-iteration</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>for-loops-and-range</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O2" t="b">
+      <c r="O12" t="b">
         <v>0</v>
       </c>
-      <c r="P2" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q2" t="b">
-        <v>1</v>
-      </c>
-      <c r="R2" t="inlineStr">
+      <c r="P12" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="b">
+        <v>1</v>
+      </c>
+      <c r="R12" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>*
 **
@@ -2720,22 +2452,22 @@
 ****</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>*</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>*
 **
@@ -2744,28 +2476,28 @@
 *****</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>*
 **</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>*
 **
@@ -2777,12 +2509,12 @@
 ********</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AD12" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AE12" t="inlineStr">
         <is>
           <t>*
 **
@@ -2792,124 +2524,117 @@
 ******</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>n = int(input())
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n = int(input())
 for i in range(1, n + 1):
-    print("*" * i)</t>
+    print("*" * i)      # row i has i stars
+</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Python - Floyd's Triangle</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>On the whiteboard in the coding club, someone has drawn Floyd's triangle: the counting numbers written out in rows, where each row holds one more number than the row above, and the counting never restarts. The club wants a program that prints the triangle for any number of rows.
 Write a program that reads a whole number `N` and prints `N` rows: row 1 has one number, row 2 has the next two, row 3 the next three, and so on, starting the count from 1 and separating the numbers in a row with single spaces.
-### Input Format
-- Line 1: N
-### Output Format
-```
-1
-2 3
-4 5 6
-```
 ### Example Walkthrough
 In the sample, `N` is 3. The counter starts at 1: row 1 takes just `1`; row 2 takes the next two numbers, `2 3`; and row 3 takes the following three, `4 5 6`. Six numbers are used in total, in unbroken counting order.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
         <v>5</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>loops-and-iteration</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>nested-loops</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O3" t="b">
+      <c r="O13" t="b">
         <v>0</v>
       </c>
-      <c r="P3" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q3" t="b">
-        <v>1</v>
-      </c>
-      <c r="R3" t="inlineStr">
+      <c r="P13" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="b">
+        <v>1</v>
+      </c>
+      <c r="R13" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>1
 2 3
 4 5 6</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>1
 2 3
@@ -2917,28 +2642,28 @@
 7 8 9 10</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>1
 2 3</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AC13" t="inlineStr">
         <is>
           <t>1
 2 3
@@ -2948,12 +2673,12 @@
 16 17 18 19 20 21</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AD13" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AE13" t="inlineStr">
         <is>
           <t>1
 2 3
@@ -2962,259 +2687,248 @@
 11 12 13 14 15</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>n = int(input())
-num = 1
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n = int(input())
+num = 1                 # next number to place, keeps increasing across rows
 for i in range(1, n + 1):
     row = []
-    for _ in range(i):
+    for _ in range(i):   # row i holds i numbers
         row.append(num)
         num += 1
-    print(*row)</t>
+    print(*row)
+</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Python - Daily Steps Total</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>A fitness app adds up a running total from day 1 to day `N`. Read `N` and print the sum of all whole numbers from 1 to `N`.
-### Input Format
-- Line 1: N, the number of days
-### Output Format
-```
-15
-```
 ### Example Walkthrough
 In the sample, `N` is `5`. Summing `1 + 2 + 3 + 4 + 5` gives `15`, so the program prints `15`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
         <v>5</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>loops-and-iteration</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>common-loop-patterns</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O4" t="b">
+      <c r="O14" t="b">
         <v>0</v>
       </c>
-      <c r="P4" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q4" t="b">
-        <v>1</v>
-      </c>
-      <c r="R4" t="inlineStr">
+      <c r="P14" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="b">
+        <v>1</v>
+      </c>
+      <c r="R14" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Y14" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AA14" t="inlineStr">
         <is>
           <t>210</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AB14" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AC14" t="inlineStr">
         <is>
           <t>1275</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AD14" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AE14" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>n = int(input())
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n = int(input())
 total = 0
 for i in range(1, n + 1):
-    total += i
-print(total)</t>
+    total += i           # running sum of 1..n
+print(total)
+</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Python - Cash Register Total</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>A shop till adds up the prices of `N` items. Read `N`, then read `N` prices on separate lines and print their total.
-### Input Format
-- Line 1: N, the number of items
-- Next N lines: one price each
-### Output Format
-```
-60
-```
 ### Example Walkthrough
 In the sample, `N` is `3` with prices `10`, `20`, and `30`. Adding them gives `60`, so the program prints `60`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
         <v>5</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>loops-and-iteration</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>common-loop-patterns</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O5" t="b">
+      <c r="O15" t="b">
         <v>0</v>
       </c>
-      <c r="P5" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" t="b">
-        <v>1</v>
-      </c>
-      <c r="R5" t="inlineStr">
+      <c r="P15" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="b">
+        <v>1</v>
+      </c>
+      <c r="R15" t="inlineStr">
         <is>
           <t>3
 10
@@ -3222,23 +2936,23 @@
 30</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>1
 5</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>4
 1
@@ -3247,24 +2961,24 @@
 4</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>2
 0
 0</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>5
 100
@@ -3274,23 +2988,23 @@
 500</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AA15" t="inlineStr">
         <is>
           <t>1500</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t>1
 999</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AC15" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AD15" t="inlineStr">
         <is>
           <t>6
 1
@@ -3301,269 +3015,255 @@
 1</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AE15" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>n = int(input())
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n = int(input())
 total = 0
-for _ in range(n):
+for _ in range(n):       # read one price per item
     total += int(input())
-print(total)</t>
+print(total)
+</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Python - Factorial Machine</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>A calculator computes the factorial of `N` (the product `1 x 2 x ... x N`; `0!` is `1`). Read `N` and print `N!`.
-### Input Format
-- Line 1: N
-### Output Format
-```
-120
-```
 ### Example Walkthrough
 In the sample, `N` is `5`. Multiplying `1 x 2 x 3 x 4 x 5` gives `120`, so the program prints `120`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
         <v>5</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>loops-and-iteration</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>common-loop-patterns</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O6" t="b">
+      <c r="O16" t="b">
         <v>0</v>
       </c>
-      <c r="P6" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q6" t="b">
-        <v>1</v>
-      </c>
-      <c r="R6" t="inlineStr">
+      <c r="P16" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="b">
+        <v>1</v>
+      </c>
+      <c r="R16" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>120</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>720</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AA16" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AB16" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AC16" t="inlineStr">
         <is>
           <t>5040</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AD16" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AE16" t="inlineStr">
         <is>
           <t>3628800</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>n = int(input())
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n = int(input())
 fact = 1
 for i in range(1, n + 1):
-    fact *= i
-print(fact)</t>
+    fact *= i             # multiply in each number up to n
+print(fact)
+</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Python - Even Numbers List</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>A number-line poster shows all even numbers up to a limit. Read `N` and print every even number from 2 up to `N`, one per line.
-### Input Format
-- Line 1: N, the upper limit
-### Output Format
-```
-2
-4
-6
-8
-10
-```
 ### Example Walkthrough
 In the sample, `N` is `10`. The even numbers from `2` up to `10` are `2, 4, 6, 8, 10`, each printed on its own line.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
         <v>5</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>loops-and-iteration</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>for-loops-and-range</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O7" t="b">
+      <c r="O17" t="b">
         <v>0</v>
       </c>
-      <c r="P7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q7" t="b">
-        <v>1</v>
-      </c>
-      <c r="R7" t="inlineStr">
+      <c r="P17" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="b">
+        <v>1</v>
+      </c>
+      <c r="R17" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>2
 4
@@ -3572,12 +3272,12 @@
 10</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>2
 4
@@ -3585,32 +3285,32 @@
 8</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AB17" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AC17" t="inlineStr">
         <is>
           <t>2
 4
@@ -3624,12 +3324,12 @@
 20</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AD17" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AE17" t="inlineStr">
         <is>
           <t>2
 4
@@ -3640,95 +3340,89 @@
 14</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>n = int(input())
-for i in range(2, n + 1, 2):
-    print(i)</t>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n = int(input())
+for i in range(2, n + 1, 2):  # start at 2, step by 2 to stay even
+    print(i)
+</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Python - Class Average</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>A teacher averages `N` test scores. Read `N`, then read `N` scores on separate lines and print their average rounded to 2 decimal places.
-### Input Format
-- Line 1: N
-- Next N lines: one score each
-### Output Format
-```
-80.0
-```
 ### Example Walkthrough
 In the sample, `N` is `3` with scores `70`, `80`, and `90`. Their average is `(70 + 80 + 90) / 3 = 80.0`, so the program prints `80.0`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
         <v>5</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>loops-and-iteration</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>common-loop-patterns</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O8" t="b">
+      <c r="O18" t="b">
         <v>0</v>
       </c>
-      <c r="P8" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q8" t="b">
-        <v>1</v>
-      </c>
-      <c r="R8" t="inlineStr">
+      <c r="P18" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q18" t="b">
+        <v>1</v>
+      </c>
+      <c r="R18" t="inlineStr">
         <is>
           <t>3
 80
@@ -3736,46 +3430,46 @@
 70</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>80.0</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>2
 50
 75</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>62.5</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>1
 42</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>42.0</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>1
 0</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>4
 60
@@ -3784,12 +3478,12 @@
 90</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AA18" t="inlineStr">
         <is>
           <t>75.0</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AB18" t="inlineStr">
         <is>
           <t>5
 100
@@ -3799,1799 +3493,1557 @@
 100</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AC18" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AD18" t="inlineStr">
         <is>
           <t>2
 33
 67</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AE18" t="inlineStr">
         <is>
           <t>50.0</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>n = int(input())
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n = int(input())
 total = 0
-for _ in range(n):
+for _ in range(n):        # read one score per student
     total += int(input())
-print(round(total / n, 2))</t>
+print(round(total / n, 2))
+</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Python - String Reverser</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>A word-game shows a word spelled backwards. Read one line and print its characters in reverse order, building the result with a loop.
-### Input Format
-- Line 1: A line of text
-### Output Format
-```
-olleh
-```
 ### Example Walkthrough
 In the sample, the input is `hello`. Reversing its characters gives `olleh`, so the program prints `olleh`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
         <v>5</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>loops-and-iteration</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>sequence-iteration</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O9" t="b">
+      <c r="O19" t="b">
         <v>0</v>
       </c>
-      <c r="P9" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q9" t="b">
-        <v>1</v>
-      </c>
-      <c r="R9" t="inlineStr">
+      <c r="P19" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q19" t="b">
+        <v>1</v>
+      </c>
+      <c r="R19" t="inlineStr">
         <is>
           <t>hello</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>olleh</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>level</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>level</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>nohtyP</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Y19" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="Z19" t="inlineStr">
         <is>
           <t>racecar</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AA19" t="inlineStr">
         <is>
           <t>racecar</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AB19" t="inlineStr">
         <is>
           <t>OpenAI</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AC19" t="inlineStr">
         <is>
           <t>IAnepO</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AD19" t="inlineStr">
         <is>
           <t>Coding</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AE19" t="inlineStr">
         <is>
           <t>gnidoC</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>text = input()
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text = input()
 result = ""
 for ch in text:
-    result = ch + result
-print(result)</t>
+    result = ch + result   # place each new char before what's built so far
+print(result)
+</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Python - Count Letter A</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>A word game show counts how many times the lowercase letter `a` appears in the word a contestant submits, since that is how many bonus points they earn. A capital `A` does not count as a match.
 Write a program that reads a line of text and prints how many times the lowercase letter `a` appears in it, scanning the text one character at a time with a loop.
-### Input Format
-- Line 1: A line of text
-### Output Format
-```
-3
-```
 ### Example Walkthrough
 In the sample, the text is `banana`. Scanning letter by letter, the lowercase `a` appears at positions 2, 4, and 6, which is 3 times, so the program prints `3`.
 ### Constraints
 - The input is a valid line of text with no leading or trailing spaces.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
         <v>5</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>loops-and-iteration</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>sequence-iteration</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O10" t="b">
+      <c r="O20" t="b">
         <v>0</v>
       </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" t="b">
-        <v>1</v>
-      </c>
-      <c r="R10" t="inlineStr">
+      <c r="P20" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q20" t="b">
+        <v>1</v>
+      </c>
+      <c r="R20" t="inlineStr">
         <is>
           <t>banana</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>apple</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>xyz</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Y20" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="Z20" t="inlineStr">
         <is>
           <t>aaaa</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AA20" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AB20" t="inlineStr">
         <is>
           <t>Ananya</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AC20" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AD20" t="inlineStr">
         <is>
           <t>data</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AE20" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>s=input()
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">s=input()
 c=0
 for ch in s:
- if ch=="a": c+=1
-print(c)</t>
+ if ch=="a": c+=1  # only lowercase a counts
+print(c)
+</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Python - Multiples List</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>A bus company wants a quick preview of the next 5 departure times once a route's interval is set: if buses run every N minutes, departures happen at N, 2N, 3N, 4N, and 5N minutes from now.
 Write a program that reads a whole number N and prints the first 5 multiples of N, separated by single spaces, on one line.
-### Input Format
-- Line 1: N
-### Output Format
-```
-2 4 6 8 10
-```
 ### Example Walkthrough
 In the sample, N is 2. The first 5 multiples of 2 are 2, 4, 6, 8, and 10, so the program prints `2 4 6 8 10`.
 ### Constraints
 - All numeric inputs are valid whole numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
         <v>5</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>loops-and-iteration</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>for-loops-and-range</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O11" t="b">
+      <c r="O21" t="b">
         <v>0</v>
       </c>
-      <c r="P11" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q11" t="b">
-        <v>1</v>
-      </c>
-      <c r="R11" t="inlineStr">
+      <c r="P21" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q21" t="b">
+        <v>1</v>
+      </c>
+      <c r="R21" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>2 4 6 8 10</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>5 10 15 20 25</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>1 2 3 4 5</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>0 0 0 0 0</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="Z21" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AA21" t="inlineStr">
         <is>
           <t>-3 -6 -9 -12 -15</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AB21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AC21" t="inlineStr">
         <is>
           <t>10 20 30 40 50</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AD21" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AE21" t="inlineStr">
         <is>
           <t>7 14 21 28 35</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>n=int(input())
-print(*[n*i for i in range(1,6)])</t>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n=int(input())
+print(*[n*i for i in range(1,6)])  # first 5 multiples: n*1 through n*5
+</t>
         </is>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AH11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>explanation</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>difficulty</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>bloomTaxonomy</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>tags</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>subjects</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>topics</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>subTopics</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>companies</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>codingType</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>language</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>supportAllLanguages</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>enablePartialScore</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>ignoreCase</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>testcase1_input</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>testcase1_output</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>testcase2_input</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>testcase2_output</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>testcase3_input</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>testcase3_output</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>testcase4_input</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>testcase4_output</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>testcase5_input</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>testcase5_output</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>testcase6_input</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>testcase6_output</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>testcase7_input</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>testcase7_output</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>preloadCode_python</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>solution_python</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>hints</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Python - Sum of Even Numbers</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>An energy meter sums only the even readings from 1 to `N`. Read `N` and print the total of all even numbers in that range.
-### Input Format
-- Line 1: N
-### Output Format
-```
-30
-```
 ### Example Walkthrough
 In the sample, `N` is `10`. The even numbers up to `10` are `2, 4, 6, 8, 10`, which add up to `30`, so the program prints `30`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
         <v>5</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>loops-and-iteration</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>common-loop-patterns</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O2" t="b">
+      <c r="O22" t="b">
         <v>0</v>
       </c>
-      <c r="P2" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q2" t="b">
-        <v>1</v>
-      </c>
-      <c r="R2" t="inlineStr">
+      <c r="P22" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q22" t="b">
+        <v>1</v>
+      </c>
+      <c r="R22" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Y22" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AA22" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AB22" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AC22" t="inlineStr">
         <is>
           <t>110</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AD22" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AE22" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>n = int(input())
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n = int(input())
 total = 0
 for i in range(1, n + 1):
     if i % 2 == 0:
-        total += i
-print(total)</t>
+        total += i         # only add even numbers
+print(total)
+</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>Python - Above the Bar</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>A results board counts how many scores beat a cut-off. Read `N`, then a line of `N` scores, then the cut-off, and print how many scores are strictly greater than the cut-off.
-### Input Format
-- Line 1: N
-- Line 2: N space-separated scores
-- Line 3: The cut-off
-### Output Format
-```
-3
-```
 ### Example Walkthrough
 In the sample, `N` is `5` with scores `50 60 70 80 90` and a cut-off of `65`. The scores strictly greater than `65` are `70`, `80`, and `90` - three in total - so the program prints `3`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
         <v>5</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>loops-and-iteration</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>common-loop-patterns</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O3" t="b">
+      <c r="O23" t="b">
         <v>0</v>
       </c>
-      <c r="P3" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q3" t="b">
-        <v>1</v>
-      </c>
-      <c r="R3" t="inlineStr">
+      <c r="P23" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q23" t="b">
+        <v>1</v>
+      </c>
+      <c r="R23" t="inlineStr">
         <is>
           <t>5
 10 20 30 40 50
 25</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>3
 1 2 3
 5</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>4
 7 8 9 10
 8</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="W23" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>1
 5
 0</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Y23" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="Z23" t="inlineStr">
         <is>
           <t>6
 -1 -2 3 4 5 6
 2</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AA23" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AB23" t="inlineStr">
         <is>
           <t>3
 100 200 300
 1000</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AC23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AD23" t="inlineStr">
         <is>
           <t>2
 5 5
 5</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AE23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>n = int(input())
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n = int(input())
 nums = list(map(int, input().split()))
 cutoff = int(input())
 count = 0
 for x in nums:
     if x &gt; cutoff:
-        count += 1
-print(count)</t>
+        count += 1          # strictly greater than cutoff counts
+print(count)
+</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Python - Highest Reading</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>A weather log finds the highest temperature of the day. Read `N`, then a line of `N` temperatures, and print the largest one using a loop.
-### Input Format
-- Line 1: N
-- Line 2: N space-separated numbers
-### Output Format
-```
-9
-```
 ### Example Walkthrough
 In the sample, `N` is `4` with readings `3 9 5 1`. The largest of these is `9`, so the program prints `9`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
         <v>5</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>loops-and-iteration</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>common-loop-patterns</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O4" t="b">
+      <c r="O24" t="b">
         <v>0</v>
       </c>
-      <c r="P4" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q4" t="b">
-        <v>1</v>
-      </c>
-      <c r="R4" t="inlineStr">
+      <c r="P24" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q24" t="b">
+        <v>1</v>
+      </c>
+      <c r="R24" t="inlineStr">
         <is>
           <t>5
 3 9 2 7 5</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>3
 -1 -5 -3</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="V24" t="inlineStr">
         <is>
           <t>1
 42</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="W24" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>2
 0 0</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Y24" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="Z24" t="inlineStr">
         <is>
           <t>4
 10 20 30 40</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AA24" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AB24" t="inlineStr">
         <is>
           <t>6
 -5 -1 -9 -3 -2 -8</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AC24" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AD24" t="inlineStr">
         <is>
           <t>3
 100 5 3</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AE24" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>n = int(input())
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n = int(input())
 nums = list(map(int, input().split()))
-largest = nums[0]
+largest = nums[0]           # start with the first value as the current best
 for x in nums[1:]:
     if x &gt; largest:
-        largest = x
-print(largest)</t>
+        largest = x          # found a new largest value
+print(largest)
+</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Python - Character Frequency</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>A text tool counts how many times a specific character appears. Read a line of text, then a single character, and print how many times that character occurs in the text.
-### Input Format
-- Line 1: A line of text
-- Line 2: A single character
-### Output Format
-```
-3
-```
 ### Example Walkthrough
 In the sample, the text is `banana` and the target character is `a`. The letter `a` appears `3` times, so the program prints `3`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
         <v>5</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>loops-and-iteration</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>sequence-iteration</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O5" t="b">
+      <c r="O25" t="b">
         <v>0</v>
       </c>
-      <c r="P5" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" t="b">
-        <v>1</v>
-      </c>
-      <c r="R5" t="inlineStr">
+      <c r="P25" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q25" t="b">
+        <v>1</v>
+      </c>
+      <c r="R25" t="inlineStr">
         <is>
           <t>banana
 a</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>mississippi
 s</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>hello
 z</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="W25" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>a
 a</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Y25" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="Z25" t="inlineStr">
         <is>
           <t>aaaaaa
 a</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AA25" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AB25" t="inlineStr">
         <is>
           <t>programming
 g</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AC25" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AD25" t="inlineStr">
         <is>
           <t>Testing
 T</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AE25" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>text = input()
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text = input()
 target = input()
 count = 0
 for ch in text:
     if ch == target:
-        count += 1
-print(count)</t>
+        count += 1            # matches the target character
+print(count)
+</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>Python - Fibonacci Terms</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>Print the first `N` terms of the Fibonacci sequence (starting `0`, `1`) on a single line, separated by spaces.
-### Input Format
-- Line 1: N, the number of terms
-### Output Format
-```
-0 1 1 2 3
-```
 ### Example Walkthrough
 In the sample, `N` is `5`. The first five terms of the sequence are `0, 1, 1, 2, 3`, so the program prints `0 1 1 2 3`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
         <v>5</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>loops-and-iteration</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>common-loop-patterns</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O6" t="b">
+      <c r="O26" t="b">
         <v>0</v>
       </c>
-      <c r="P6" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q6" t="b">
-        <v>1</v>
-      </c>
-      <c r="R6" t="inlineStr">
+      <c r="P26" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q26" t="b">
+        <v>1</v>
+      </c>
+      <c r="R26" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>0 1 1 2 3</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="V26" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="W26" t="inlineStr">
         <is>
           <t>0 1 1 2 3 5 8 13</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="Z26" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AA26" t="inlineStr">
         <is>
           <t>0 1</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AB26" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AC26" t="inlineStr">
         <is>
           <t>0 1 1 2 3 5 8 13 21 34 55 89</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AD26" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AE26" t="inlineStr">
         <is>
           <t>0 1 1 2 3 5 8 13 21 34</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>n = int(input())
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n = int(input())
 a, b = 0, 1
 result = []
 for _ in range(n):
-    result.append(a)
-    a, b = b, a + b
-print(*result)</t>
+    result.append(a)          # a is the current term
+    a, b = b, a + b            # advance both terms together
+print(*result)
+</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>Python - Reverse a Number</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>Read a whole number and print it with its digits reversed (drop any leading zeros that result).
-### Input Format
-- Line 1: A whole number
-### Output Format
-```
-4321
-```
 ### Example Walkthrough
 In the sample, the number is `1234`. Reversing its digits gives `4321`, so the program prints `4321`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
         <v>5</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>loops-and-iteration</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>while-loops</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O7" t="b">
+      <c r="O27" t="b">
         <v>0</v>
       </c>
-      <c r="P7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q7" t="b">
-        <v>1</v>
-      </c>
-      <c r="R7" t="inlineStr">
+      <c r="P27" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q27" t="b">
+        <v>1</v>
+      </c>
+      <c r="R27" t="inlineStr">
         <is>
           <t>1234</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>4321</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="U27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="V27" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="W27" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Y27" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="Z27" t="inlineStr">
         <is>
           <t>-89</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AA27" t="inlineStr">
         <is>
           <t>-98</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AB27" t="inlineStr">
         <is>
           <t>987654</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AC27" t="inlineStr">
         <is>
           <t>456789</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AD27" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AE27" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>n = int(input())
-sign = -1 if n &lt; 0 else 1
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n = int(input())
+sign = -1 if n &lt; 0 else 1     # remember the sign to reapply later
 n = abs(n)
 rev = 0
 while n &gt; 0:
-    rev = rev * 10 + n % 10
-    n //= 10
-print(sign * rev)</t>
+    rev = rev * 10 + n % 10    # shift left and add the last digit
+    n //= 10                    # drop the last digit
+print(sign * rev)
+</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Python - Multiplication Grid</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>Print an `N` by `N` grid where the cell in row `i`, column `j` holds `i x j`. Separate values in a row with single spaces.
-### Input Format
-- Line 1: N
-### Output Format
-```
-1 2 3
-2 4 6
-3 6 9
-```
 ### Example Walkthrough
 In the sample, `N` is `3`. Row `1` holds `1 2 3`, row `2` holds `2 4 6`, and row `3` holds `3 6 9`, each value being the row number times the column number.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
         <v>5</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>loops-and-iteration</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>nested-loops</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O8" t="b">
+      <c r="O28" t="b">
         <v>0</v>
       </c>
-      <c r="P8" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q8" t="b">
-        <v>1</v>
-      </c>
-      <c r="R8" t="inlineStr">
+      <c r="P28" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q28" t="b">
+        <v>1</v>
+      </c>
+      <c r="R28" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>1 2 3
 2 4 6
 3 6 9</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U28" t="inlineStr">
         <is>
           <t>1 2
 2 4</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="V28" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="W28" t="inlineStr">
         <is>
           <t>1 2 3 4
 2 4 6 8
@@ -5599,27 +5051,27 @@
 4 8 12 16</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Y28" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="Z28" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AB28" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AC28" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6
 2 4 6 8 10 12
@@ -5629,12 +5081,12 @@
 6 12 18 24 30 36</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AD28" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AE28" t="inlineStr">
         <is>
           <t>1 2 3 4 5
 2 4 6 8 10
@@ -5643,447 +5095,430 @@
 5 10 15 20 25</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>n = int(input())
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n = int(input())
 for i in range(1, n + 1):
     row = []
     for j in range(1, n + 1):
-        row.append(i * j)
-    print(*row)</t>
+        row.append(i * j)       # value at row i, column j
+    print(*row)
+</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>Python - First Negative Stop</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>A vending machine adds up the value of coins as they are inserted one by one, but stops counting the instant its sensor reports an invalid (negative) reading, without adding that faulty reading to the total.
 Write a program that reads a line of whole numbers separated by spaces and adds them up one at a time using a loop, stopping (without adding it) as soon as a negative number is seen. Print the total collected so far.
-### Input Format
-- Line 1: Whole numbers separated by spaces
-### Output Format
-```
-3
-```
 ### Example Walkthrough
 In the sample, the numbers are `1 2 -1 5`. The loop adds 1, then 2, reaching a total of 3, then sees -1 and stops immediately without adding it or looking at the remaining 5. The program prints `3`.
 ### Constraints
 - All numeric inputs are valid whole numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
         <v>5</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>loops-and-iteration</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>loop-control-statements</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O9" t="b">
+      <c r="O29" t="b">
         <v>0</v>
       </c>
-      <c r="P9" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q9" t="b">
-        <v>1</v>
-      </c>
-      <c r="R9" t="inlineStr">
+      <c r="P29" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q29" t="b">
+        <v>1</v>
+      </c>
+      <c r="R29" t="inlineStr">
         <is>
           <t>1 2 -1 5</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>5 5 5</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U29" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="V29" t="inlineStr">
         <is>
           <t>-1 2 3</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="W29" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>0 -2</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Y29" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="Z29" t="inlineStr">
         <is>
           <t>10 -5 10</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AA29" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AB29" t="inlineStr">
         <is>
           <t>3 4 5 -9</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AC29" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AD29" t="inlineStr">
         <is>
           <t>1 0 2</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AE29" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>total=0
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">total=0
 for x in map(int,input().split()):
- if x&lt;0: break
+ if x&lt;0: break  # stop as soon as a negative value appears
  total+=x
-print(total)</t>
+print(total)
+</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>Python - Find Minimum</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>A weather app scans a list of temperature readings taken through the day and reports the lowest one, so the evening news can announce the day's coldest moment.
 Write a program that reads a line of whole numbers separated by spaces and prints the smallest one, found using a loop that compares each value to the smallest seen so far.
-### Input Format
-- Line 1: Whole numbers separated by spaces
-### Output Format
-```
-1
-```
 ### Example Walkthrough
 In the sample, the numbers are `3 1 4`. Starting with 3 as the smallest seen so far, the loop compares it to 1 (smaller, so 1 becomes the smallest) and then to 4 (not smaller), leaving 1 as the overall minimum. The program prints `1`.
 ### Constraints
 - All numeric inputs are valid whole numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
         <v>5</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>loops-and-iteration</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>common-loop-patterns</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O10" t="b">
+      <c r="O30" t="b">
         <v>0</v>
       </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" t="b">
-        <v>1</v>
-      </c>
-      <c r="R10" t="inlineStr">
+      <c r="P30" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q30" t="b">
+        <v>1</v>
+      </c>
+      <c r="R30" t="inlineStr">
         <is>
           <t>3 1 4</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="V30" t="inlineStr">
         <is>
           <t>0 -1 2</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="W30" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>100 50 25</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Y30" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="Z30" t="inlineStr">
         <is>
           <t>7 7 7</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AA30" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AB30" t="inlineStr">
         <is>
           <t>-5 -9 -1</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AC30" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AD30" t="inlineStr">
         <is>
           <t>10 9 8 7</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AE30" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>nums=list(map(int,input().split()))
-b=nums[0]
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nums=list(map(int,input().split()))
+b=nums[0]                 # start with the first value as the current smallest
 for x in nums:
- if x&lt;b: b=x
-print(b)</t>
+ if x&lt;b: b=x  # found a smaller value, update the running minimum
+print(b)
+</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>Python - Number Triangle</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>A lecture hall's seating-chart generator prints an increasing triangle of numbers to show students how seats fill up row by row: row 1 shows just seat 1, row 2 shows seats 1 and 2, and so on up to row N.
 Write a program that reads a whole number N and, using nested loops, prints N rows where row `i` contains the numbers from 1 to `i` separated by single spaces, each row on its own line.
-### Input Format
-- Line 1: N
-### Output Format
-```
-1
-1 2
-1 2 3
-```
 ### Example Walkthrough
 In the sample, N is 3. The outer loop runs for rows 1 through 3: row 1 prints just `1`, row 2 prints `1 2`, and row 3 prints `1 2 3`, giving three lines that grow by one number each time.
 ### Constraints
 - All numeric inputs are valid whole numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
         <v>5</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>loops-and-iteration</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>nested-loops</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O11" t="b">
+      <c r="O31" t="b">
         <v>0</v>
       </c>
-      <c r="P11" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q11" t="b">
-        <v>1</v>
-      </c>
-      <c r="R11" t="inlineStr">
+      <c r="P31" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q31" t="b">
+        <v>1</v>
+      </c>
+      <c r="R31" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>1
 1 2
 1 2 3</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T31" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U31" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V31" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="W31" t="inlineStr">
         <is>
           <t>1
 1 2
@@ -6091,17 +5526,17 @@
 1 2 3 4</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="Z31" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AA31" t="inlineStr">
         <is>
           <t>1
 1 2
@@ -6110,23 +5545,23 @@
 1 2 3 4 5</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AB31" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AC31" t="inlineStr">
         <is>
           <t>1
 1 2</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AD31" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AE31" t="inlineStr">
         <is>
           <t>1
 1 2
@@ -6136,649 +5571,444 @@
 1 2 3 4 5 6</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>n=int(input())
-for i in range(1,n+1): print(*range(1,i+1))</t>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n=int(input())
+for i in range(1,n+1): print(*range(1,i+1))  # row i lists seats 1 through i
+</t>
         </is>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AH11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>explanation</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>difficulty</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>bloomTaxonomy</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>tags</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>subjects</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>topics</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>subTopics</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>companies</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>codingType</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>language</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>supportAllLanguages</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>enablePartialScore</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>ignoreCase</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>testcase1_input</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>testcase1_output</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>testcase2_input</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>testcase2_output</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>testcase3_input</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>testcase3_output</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>testcase4_input</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>testcase4_output</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>testcase5_input</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>testcase5_output</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>testcase6_input</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>testcase6_output</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>testcase7_input</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>testcase7_output</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>preloadCode_python</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>solution_python</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>hints</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>Python - Count the Primes</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>Read `N` and print how many prime numbers there are from 2 up to and including `N`.
-### Input Format
-- Line 1: N
-### Output Format
-```
-4
-```
 ### Example Walkthrough
 In the sample, `N` is `10`. The primes from `2` to `10` are `2, 3, 5, 7` - four in total - so the program prints `4`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
         <v>5</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>loops-and-iteration</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>nested-loops</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O2" t="b">
+      <c r="O32" t="b">
         <v>0</v>
       </c>
-      <c r="P2" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q2" t="b">
-        <v>1</v>
-      </c>
-      <c r="R2" t="inlineStr">
+      <c r="P32" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q32" t="b">
+        <v>1</v>
+      </c>
+      <c r="R32" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T32" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U32" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="V32" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="W32" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Y32" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="Z32" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AA32" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AB32" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AC32" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AD32" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AE32" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>n = int(input())
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n = int(input())
 count = 0
 for num in range(2, n + 1):
     is_prime = True
-    for i in range(2, int(num ** 0.5) + 1):
+    for i in range(2, int(num ** 0.5) + 1):  # only need to check up to sqrt(num)
         if num % i == 0:
             is_prime = False
-            break
+            break                # found a divisor, stop checking
     if is_prime:
         count += 1
-print(count)</t>
+print(count)
+</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>Python - Pairs That Add Up</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>Read `N`, a line of `N` numbers, and a target. Count how many pairs of positions (`i` before `j`) have values that add up to the target.
-### Input Format
-- Line 1: N
-- Line 2: N space-separated numbers
-- Line 3: Target
-### Output Format
-```
-2
-```
 ### Example Walkthrough
 In the sample, `N` is `5` with numbers `1 2 3 4 5` and a target of `6`. The pairs `(1, 5)` and `(2, 4)` both add up to `6` - two pairs in total - so the program prints `2`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
         <v>5</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>loops-and-iteration</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>nested-loops</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O3" t="b">
+      <c r="O33" t="b">
         <v>0</v>
       </c>
-      <c r="P3" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q3" t="b">
-        <v>1</v>
-      </c>
-      <c r="R3" t="inlineStr">
+      <c r="P33" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q33" t="b">
+        <v>1</v>
+      </c>
+      <c r="R33" t="inlineStr">
         <is>
           <t>4
 1 2 3 4
 5</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S33" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T33" t="inlineStr">
         <is>
           <t>3
 1 1 1
 2</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U33" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="V33" t="inlineStr">
         <is>
           <t>3
 5 6 7
 100</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="W33" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>1
 5
 5</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Y33" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="Z33" t="inlineStr">
         <is>
           <t>2
 0 0
 0</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AA33" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AB33" t="inlineStr">
         <is>
           <t>6
 1 2 3 4 5 6
 7</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AC33" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AD33" t="inlineStr">
         <is>
           <t>5
 -1 -2 3 4 5
 2</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AE33" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>n = int(input())
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n = int(input())
 nums = list(map(int, input().split()))
 target = int(input())
 count = 0
 for i in range(n):
-    for j in range(i + 1, n):
+    for j in range(i + 1, n):    # j starts after i so pairs aren't repeated
         if nums[i] + nums[j] == target:
             count += 1
-print(count)</t>
+print(count)
+</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>Python - Row Totals</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>Read a grid with `R` rows and `C` columns, then print the sum of each row on its own line, top to bottom.
-### Input Format
-- Line 1: R and C separated by a space
-- Next R lines: C space-separated numbers each
-### Output Format
-```
-6
-15
-```
 ### Example Walkthrough
 In the sample, the grid is `2` rows by `3` columns: `1 2 3` and `4 5 6`. The first row sums to `6` and the second sums to `15`, so the program prints `6` then `15`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
         <v>5</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>loops-and-iteration</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>common-loop-patterns</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O4" t="b">
+      <c r="O34" t="b">
         <v>0</v>
       </c>
-      <c r="P4" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q4" t="b">
-        <v>1</v>
-      </c>
-      <c r="R4" t="inlineStr">
+      <c r="P34" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q34" t="b">
+        <v>1</v>
+      </c>
+      <c r="R34" t="inlineStr">
         <is>
           <t>2 3
 1 2 3
 4 5 6</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t>6
 15</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T34" t="inlineStr">
         <is>
           <t>1 1
 99</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U34" t="inlineStr">
         <is>
           <t>99</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="V34" t="inlineStr">
         <is>
           <t>3 2
 1 1
@@ -6786,38 +6016,38 @@
 3 3</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="W34" t="inlineStr">
         <is>
           <t>2
 4
 6</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="X34" t="inlineStr">
         <is>
           <t>1 1
 0</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Y34" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="Z34" t="inlineStr">
         <is>
           <t>2 2
 -1 -2
 -3 -4</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AA34" t="inlineStr">
         <is>
           <t>-3
 -7</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AB34" t="inlineStr">
         <is>
           <t>4 1
 5
@@ -6826,7 +6056,7 @@
 20</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AC34" t="inlineStr">
         <is>
           <t>5
 10
@@ -6834,7 +6064,7 @@
 20</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AD34" t="inlineStr">
         <is>
           <t>3 3
 1 2 3
@@ -6842,110 +6072,102 @@
 7 8 9</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AE34" t="inlineStr">
         <is>
           <t>6
 15
 24</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>r, c = map(int, input().split())
-for _ in range(r):
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">r, c = map(int, input().split())
+for _ in range(r):               # process one row at a time
     nums = list(map(int, input().split()))
-    print(sum(nums))</t>
+    print(sum(nums))
+</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>Python - Inverted Star Triangle</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>Print an inverted triangle of stars with `N` rows: the first row has `N` stars and each row below has one fewer, down to a single star.
-### Input Format
-- Line 1: N
-### Output Format
-```
-****
-***
-**
-*
-```
 ### Example Walkthrough
 In the sample, `N` is `4`. The rows have `4`, `3`, `2`, and `1` stars, printing `****`, `***`, `**`, and `*` in that order.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
         <v>5</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>loops-and-iteration</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>for-loops-and-range</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O5" t="b">
+      <c r="O35" t="b">
         <v>0</v>
       </c>
-      <c r="P5" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" t="b">
-        <v>1</v>
-      </c>
-      <c r="R5" t="inlineStr">
+      <c r="P35" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q35" t="b">
+        <v>1</v>
+      </c>
+      <c r="R35" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="S35" t="inlineStr">
         <is>
           <t>****
 ***
@@ -6953,50 +6175,50 @@
 *</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T35" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="U35" t="inlineStr">
         <is>
           <t>*</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="V35" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="W35" t="inlineStr">
         <is>
           <t>***
 **
 *</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="X35" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Y35" t="inlineStr">
         <is>
           <t>**
 *</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="Z35" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AB35" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AC35" t="inlineStr">
         <is>
           <t>*******
 ******
@@ -7007,12 +6229,12 @@
 *</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AD35" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AE35" t="inlineStr">
         <is>
           <t>******
 *****
@@ -7022,144 +6244,137 @@
 *</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>n = int(input())
-for i in range(n, 0, -1):
-    print("*" * i)</t>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n = int(input())
+for i in range(n, 0, -1):        # star count shrinks from n down to 1
+    print("*" * i)
+</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>Python - Student Averages</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>Read `N` and `M`, then `N` lines each holding `M` marks. For each student print their average mark rounded to 2 decimal places, one per line.
-### Input Format
-- Line 1: N (students) and M (subjects), space-separated
-- Next N lines: M space-separated marks each
-### Output Format
-```
-90.0
-70.0
-```
 ### Example Walkthrough
 In the sample, `N` is `2` and `M` is `2`. The first student's marks are `90 90`, averaging to `90.0`, and the second student's marks are `70 70`, averaging to `70.0`, so the program prints `90.0` then `70.0`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
         <v>5</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>loops-and-iteration</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>common-loop-patterns</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O6" t="b">
+      <c r="O36" t="b">
         <v>0</v>
       </c>
-      <c r="P6" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q6" t="b">
-        <v>1</v>
-      </c>
-      <c r="R6" t="inlineStr">
+      <c r="P36" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q36" t="b">
+        <v>1</v>
+      </c>
+      <c r="R36" t="inlineStr">
         <is>
           <t>2 3
 80 90 100
 60 70 80</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S36" t="inlineStr">
         <is>
           <t>90.0
 70.0</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T36" t="inlineStr">
         <is>
           <t>1 2
 50 75</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U36" t="inlineStr">
         <is>
           <t>62.5</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="V36" t="inlineStr">
         <is>
           <t>2 2
 100 100
 0 0</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="W36" t="inlineStr">
         <is>
           <t>100.0
 0.0</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="X36" t="inlineStr">
         <is>
           <t>1 1
 0</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Y36" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="Z36" t="inlineStr">
         <is>
           <t>3 2
 10 20
@@ -7167,25 +6382,25 @@
 50 60</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AA36" t="inlineStr">
         <is>
           <t>15.0
 35.0
 55.0</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AB36" t="inlineStr">
         <is>
           <t>1 4
 90 80 70 60</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AC36" t="inlineStr">
         <is>
           <t>75.0</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AD36" t="inlineStr">
         <is>
           <t>4 3
 1 2 3
@@ -7194,7 +6409,7 @@
 10 11 12</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AE36" t="inlineStr">
         <is>
           <t>2.0
 5.0
@@ -7202,124 +6417,117 @@
 11.0</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>n, m = map(int, input().split())
-for _ in range(n):
+      <c r="AG36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n, m = map(int, input().split())
+for _ in range(n):                # process one student at a time
     marks = list(map(int, input().split()))
-    print(round(sum(marks) / m, 2))</t>
+    print(round(sum(marks) / m, 2))
+</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>Python - Repeated Digit Triangle</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>Print a triangle with `N` rows where row `i` shows the digit `i` repeated `i` times (for example row 3 is `333`). `N` is at most 9.
-### Input Format
-- Line 1: N (1 to 9)
-### Output Format
-```
-1
-22
-333
-```
 ### Example Walkthrough
 In the sample, `N` is `3`. Row `1` is `1`, row `2` is `22`, and row `3` is `333`, each digit repeated as many times as its row number.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
         <v>5</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>loops-and-iteration</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>for-loops-and-range</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O7" t="b">
+      <c r="O37" t="b">
         <v>0</v>
       </c>
-      <c r="P7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q7" t="b">
-        <v>1</v>
-      </c>
-      <c r="R7" t="inlineStr">
+      <c r="P37" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q37" t="b">
+        <v>1</v>
+      </c>
+      <c r="R37" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="S37" t="inlineStr">
         <is>
           <t>1
 22
 333</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="T37" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="U37" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="V37" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="W37" t="inlineStr">
         <is>
           <t>1
 22
@@ -7328,23 +6536,23 @@
 55555</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="X37" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Y37" t="inlineStr">
         <is>
           <t>1
 22</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="Z37" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AA37" t="inlineStr">
         <is>
           <t>1
 22
@@ -7357,12 +6565,12 @@
 999999999</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AB37" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AC37" t="inlineStr">
         <is>
           <t>1
 22
@@ -7373,12 +6581,12 @@
 7777777</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AD37" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AE37" t="inlineStr">
         <is>
           <t>1
 22
@@ -7386,141 +6594,135 @@
 4444</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>n = int(input())
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n = int(input())
 for i in range(1, n + 1):
-    print(str(i) * i)</t>
+    print(str(i) * i)             # row i repeats digit i, i times
+</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>Python - Biggest in the Grid</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>Read a grid with `R` rows and `C` columns and print the single largest value found anywhere in the grid.
-### Input Format
-- Line 1: R and C separated by a space
-- Next R lines: C space-separated numbers each
-### Output Format
-```
-9
-```
 ### Example Walkthrough
 In the sample, the grid is `2` rows by `2` columns: `3 9` and `5 1`. The largest value anywhere in the grid is `9`, so the program prints `9`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
         <v>5</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>loops-and-iteration</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>nested-loops</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O8" t="b">
+      <c r="O38" t="b">
         <v>0</v>
       </c>
-      <c r="P8" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q8" t="b">
-        <v>1</v>
-      </c>
-      <c r="R8" t="inlineStr">
+      <c r="P38" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q38" t="b">
+        <v>1</v>
+      </c>
+      <c r="R38" t="inlineStr">
         <is>
           <t>2 3
 1 5 3
 9 2 4</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="S38" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="T38" t="inlineStr">
         <is>
           <t>1 1
 7</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U38" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="V38" t="inlineStr">
         <is>
           <t>2 2
 -1 -2
 -3 -4</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="W38" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="X38" t="inlineStr">
         <is>
           <t>1 1
 0</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Y38" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="Z38" t="inlineStr">
         <is>
           <t>3 3
 1 2 3
@@ -7528,23 +6730,23 @@
 7 8 9</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AA38" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AB38" t="inlineStr">
         <is>
           <t>1 4
 10 20 30 40</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AC38" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AD38" t="inlineStr">
         <is>
           <t>4 1
 -5
@@ -7553,297 +6755,285 @@
 -20</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AE38" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>r, c = map(int, input().split())
+      <c r="AG38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">r, c = map(int, input().split())
 best = None
 for _ in range(r):
     nums = list(map(int, input().split()))
     for x in nums:
         if best is None or x &gt; best:
-            best = x
-print(best)</t>
+            best = x                # track the largest value seen so far
+print(best)
+</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>Python - Prime Range Count</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>A number-theory quiz app reveals a fun fact after each round: how many prime numbers exist from 2 up to whatever limit N the player chose.
 Write a program that reads a whole number N and prints how many prime numbers there are from 2 up to and including N. A prime number is a whole number greater than 1 that no smaller number (except 1) divides exactly.
-### Input Format
-- Line 1: N
-### Output Format
-```
-4
-```
 ### Example Walkthrough
 In the sample, N is 10. The prime numbers from 2 to 10 are 2, 3, 5, and 7 — four of them — so the program prints `4`.
 ### Constraints
 - All numeric inputs are valid whole numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
         <v>5</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>loops-and-iteration</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>nested-loops</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O9" t="b">
+      <c r="O39" t="b">
         <v>0</v>
       </c>
-      <c r="P9" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q9" t="b">
-        <v>1</v>
-      </c>
-      <c r="R9" t="inlineStr">
+      <c r="P39" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q39" t="b">
+        <v>1</v>
+      </c>
+      <c r="R39" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S39" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="T39" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U39" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="V39" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="W39" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="X39" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Y39" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="Z39" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AA39" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AB39" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AC39" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AD39" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AE39" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>n=int(input())
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n=int(input())
 c=0
 for x in range(2,n+1):
  p=True
- for d in range(2,x):
-  if x%d==0: p=False; break
- if p: c+=1
-print(c)</t>
+ for d in range(2,x):           # check every smaller number as a possible divisor
+  if x%d==0: p=False; break  # found a divisor, x is not prime
+ if p: c+=1  # x had no divisors, it's prime
+print(c)
+</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Python - Grid Border Stars</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>A game designer is prototyping a square arena using text characters before building real art: the outer wall is drawn with stars and the open floor space inside is drawn with dots, on an N x N grid.
 Write a program that reads a whole number N and, using nested loops, prints an N x N grid where every cell on the outer border (first row, last row, first column, or last column) is `*` and every other cell is `.`, one row per line with no spaces between characters.
-### Input Format
-- Line 1: N
-### Output Format
-```
-***
-*.*
-***
-```
 ### Example Walkthrough
 In the sample, N is 3. Every cell in the first row, last row, first column, or last column is part of the border, so the top and bottom rows are all stars (`***`) and the middle row has stars only at its two ends (`*.*`).
 ### Constraints
 - All numeric inputs are valid whole numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
         <v>5</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>loops-and-iteration</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>nested-loops</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O10" t="b">
+      <c r="O40" t="b">
         <v>0</v>
       </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" t="b">
-        <v>1</v>
-      </c>
-      <c r="R10" t="inlineStr">
+      <c r="P40" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q40" t="b">
+        <v>1</v>
+      </c>
+      <c r="R40" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="S40" t="inlineStr">
         <is>
           <t>***
 *.*
 ***</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="T40" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U40" t="inlineStr">
         <is>
           <t>*</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="V40" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="W40" t="inlineStr">
         <is>
           <t>****
 *..*
@@ -7851,12 +7041,12 @@
 ****</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="X40" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Y40" t="inlineStr">
         <is>
           <t>*****
 *...*
@@ -7865,23 +7055,23 @@
 *****</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="Z40" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AA40" t="inlineStr">
         <is>
           <t>**
 **</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AB40" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AC40" t="inlineStr">
         <is>
           <t>******
 *....*
@@ -7891,12 +7081,12 @@
 ******</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AD40" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AE40" t="inlineStr">
         <is>
           <t>*******
 *.....*
@@ -7907,173 +7097,169 @@
 *******</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>n=int(input())
+      <c r="AG40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n=int(input())
 for r in range(n):
  row=""
- for c in range(n): row += "*" if r==0 or c==0 or r==n-1 or c==n-1 else "."
- print(row)</t>
+ for c in range(n): row += "*" if r==0 or c==0 or r==n-1 or c==n-1 else "."  # star on the border, dot inside
+ print(row)
+</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>Python - Digit Product</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>A puzzle app computes a "lucky number" for each ticket by multiplying together all of its digits, so a ticket containing a 0 anywhere always ends up with a lucky number of 0.
 Write a program that reads a whole number and prints the product of its digits, found using a loop that repeatedly takes the last digit (the remainder when dividing by 10) and removes it from the number. If the number itself is 0, print `0`.
-### Input Format
-- Line 1: A whole number
-### Output Format
-```
-6
-```
 ### Example Walkthrough
 In the sample, the number is 123. Its digits are 1, 2, and 3, and multiplying them gives 1 x 2 x 3 = 6, so the program prints `6`.
 ### Constraints
 - All numeric inputs are valid whole numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
         <v>5</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>loops-and-iteration</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>while-loops</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O11" t="b">
+      <c r="O41" t="b">
         <v>0</v>
       </c>
-      <c r="P11" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q11" t="b">
-        <v>1</v>
-      </c>
-      <c r="R11" t="inlineStr">
+      <c r="P41" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q41" t="b">
+        <v>1</v>
+      </c>
+      <c r="R41" t="inlineStr">
         <is>
           <t>123</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S41" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T41" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U41" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V41" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="W41" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X41" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Y41" t="inlineStr">
         <is>
           <t>729</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="Z41" t="inlineStr">
         <is>
           <t>204</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AA41" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AB41" t="inlineStr">
         <is>
           <t>1111</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AC41" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AD41" t="inlineStr">
         <is>
           <t>808</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AE41" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>n=int(input())
-prod=0 if n==0 else 1
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n=int(input())
+prod=0 if n==0 else 1     # a lone 0 should give a product of 0
 while n&gt;0:
- prod*=n%10; n//=10
-print(prod)</t>
+ prod*=n%10; n//=10  # multiply in the last digit, then drop it
+print(prod)
+</t>
         </is>
       </c>
     </row>
